--- a/Excel/HideProListConfig.xlsx
+++ b/Excel/HideProListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7F7C97-3846-4EF8-AEDB-E00EED41190B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D39CC7-340F-439E-8CF7-59038C58C6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HideProListProto" sheetId="1" r:id="rId1"/>
@@ -350,7 +350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="115">
   <si>
     <t>Id</t>
   </si>
@@ -703,6 +703,10 @@
   </si>
   <si>
     <t>NeedNumber</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>3001,3002,3003</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1921,7 +1925,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1943,6 +1947,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2590,7 +2597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:P123"/>
+  <dimension ref="B1:P145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="11.375" customWidth="1"/>
@@ -7874,94 +7881,847 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="C122" s="8">
+    <row r="122" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C122" s="6">
+        <v>10001</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E122" s="6">
+        <v>10002</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G122" s="6">
+        <v>0</v>
+      </c>
+      <c r="H122" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="I122" s="6">
+        <v>105101</v>
+      </c>
+      <c r="J122" s="6">
+        <v>1</v>
+      </c>
+      <c r="K122" s="6">
+        <v>1</v>
+      </c>
+      <c r="L122" s="6">
+        <v>1</v>
+      </c>
+      <c r="M122" s="6">
+        <v>5</v>
+      </c>
+      <c r="N122" s="6">
+        <v>0</v>
+      </c>
+      <c r="O122" s="6">
+        <v>0</v>
+      </c>
+      <c r="P122" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C123" s="6">
+        <v>10002</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E123" s="6">
+        <v>10003</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G123" s="6">
+        <v>0</v>
+      </c>
+      <c r="H123" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="I123" s="6">
+        <v>105301</v>
+      </c>
+      <c r="J123" s="6">
+        <v>1</v>
+      </c>
+      <c r="K123" s="6">
+        <v>1</v>
+      </c>
+      <c r="L123" s="6">
+        <v>1</v>
+      </c>
+      <c r="M123" s="6">
+        <v>5</v>
+      </c>
+      <c r="N123" s="6">
+        <v>0</v>
+      </c>
+      <c r="O123" s="6">
+        <v>0</v>
+      </c>
+      <c r="P123" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C124" s="6">
+        <v>10003</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E124" s="6">
+        <v>10004</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G124" s="6">
+        <v>0</v>
+      </c>
+      <c r="H124" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="I124" s="6">
+        <v>105501</v>
+      </c>
+      <c r="J124" s="6">
+        <v>1</v>
+      </c>
+      <c r="K124" s="6">
+        <v>1</v>
+      </c>
+      <c r="L124" s="6">
+        <v>1</v>
+      </c>
+      <c r="M124" s="6">
+        <v>5</v>
+      </c>
+      <c r="N124" s="6">
+        <v>0</v>
+      </c>
+      <c r="O124" s="6">
+        <v>0</v>
+      </c>
+      <c r="P124" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C125" s="6">
+        <v>10004</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E125" s="6">
+        <v>10005</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G125" s="6">
+        <v>0</v>
+      </c>
+      <c r="H125" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="I125" s="6">
+        <v>105401</v>
+      </c>
+      <c r="J125" s="6">
+        <v>1</v>
+      </c>
+      <c r="K125" s="6">
+        <v>1</v>
+      </c>
+      <c r="L125" s="6">
+        <v>1</v>
+      </c>
+      <c r="M125" s="6">
+        <v>5</v>
+      </c>
+      <c r="N125" s="6">
+        <v>0</v>
+      </c>
+      <c r="O125" s="6">
+        <v>0</v>
+      </c>
+      <c r="P125" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C126" s="6">
+        <v>10005</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E126" s="6">
+        <v>10006</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G126" s="6">
+        <v>0</v>
+      </c>
+      <c r="H126" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I126" s="6">
+        <v>200101</v>
+      </c>
+      <c r="J126" s="6">
+        <v>0</v>
+      </c>
+      <c r="K126" s="6">
+        <v>0</v>
+      </c>
+      <c r="L126" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M126" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N126" s="6">
+        <v>0</v>
+      </c>
+      <c r="O126" s="6">
+        <v>0</v>
+      </c>
+      <c r="P126" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C127" s="6">
+        <v>10006</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E127" s="6">
+        <v>10007</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G127" s="6">
+        <v>0</v>
+      </c>
+      <c r="H127" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I127" s="6">
+        <v>200201</v>
+      </c>
+      <c r="J127" s="6">
+        <v>0</v>
+      </c>
+      <c r="K127" s="6">
+        <v>0</v>
+      </c>
+      <c r="L127" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M127" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N127" s="6">
+        <v>0</v>
+      </c>
+      <c r="O127" s="6">
+        <v>0</v>
+      </c>
+      <c r="P127" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C128" s="6">
+        <v>10007</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E128" s="6">
+        <v>10008</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G128" s="6">
+        <v>0</v>
+      </c>
+      <c r="H128" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I128" s="6">
+        <v>200301</v>
+      </c>
+      <c r="J128" s="6">
+        <v>0</v>
+      </c>
+      <c r="K128" s="6">
+        <v>0</v>
+      </c>
+      <c r="L128" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M128" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N128" s="6">
+        <v>0</v>
+      </c>
+      <c r="O128" s="6">
+        <v>0</v>
+      </c>
+      <c r="P128" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C129" s="6">
+        <v>10008</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E129" s="6">
+        <v>10009</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G129" s="6">
+        <v>0</v>
+      </c>
+      <c r="H129" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I129" s="6">
+        <v>200401</v>
+      </c>
+      <c r="J129" s="6">
+        <v>0</v>
+      </c>
+      <c r="K129" s="6">
+        <v>0</v>
+      </c>
+      <c r="L129" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M129" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N129" s="6">
+        <v>0</v>
+      </c>
+      <c r="O129" s="6">
+        <v>0</v>
+      </c>
+      <c r="P129" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C130" s="6">
+        <v>10009</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E130" s="6">
+        <v>10010</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G130" s="6">
+        <v>0</v>
+      </c>
+      <c r="H130" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I130" s="6">
+        <v>202101</v>
+      </c>
+      <c r="J130" s="6">
+        <v>0</v>
+      </c>
+      <c r="K130" s="6">
+        <v>0</v>
+      </c>
+      <c r="L130" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M130" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N130" s="6">
+        <v>0</v>
+      </c>
+      <c r="O130" s="6">
+        <v>0</v>
+      </c>
+      <c r="P130" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C131" s="6">
+        <v>10010</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E131" s="6">
+        <v>10011</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G131" s="6">
+        <v>0</v>
+      </c>
+      <c r="H131" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I131" s="6">
+        <v>200501</v>
+      </c>
+      <c r="J131" s="6">
+        <v>0</v>
+      </c>
+      <c r="K131" s="6">
+        <v>0</v>
+      </c>
+      <c r="L131" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M131" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N131" s="6">
+        <v>0</v>
+      </c>
+      <c r="O131" s="6">
+        <v>0</v>
+      </c>
+      <c r="P131" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C132" s="6">
+        <v>10011</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E132" s="6">
+        <v>10012</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G132" s="6">
+        <v>0</v>
+      </c>
+      <c r="H132" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I132" s="6">
+        <v>200601</v>
+      </c>
+      <c r="J132" s="6">
+        <v>0</v>
+      </c>
+      <c r="K132" s="6">
+        <v>0</v>
+      </c>
+      <c r="L132" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M132" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N132" s="6">
+        <v>0</v>
+      </c>
+      <c r="O132" s="6">
+        <v>0</v>
+      </c>
+      <c r="P132" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C133" s="6">
+        <v>10012</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E133" s="6">
+        <v>10013</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G133" s="6">
+        <v>0</v>
+      </c>
+      <c r="H133" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I133" s="6">
+        <v>200701</v>
+      </c>
+      <c r="J133" s="6">
+        <v>0</v>
+      </c>
+      <c r="K133" s="6">
+        <v>0</v>
+      </c>
+      <c r="L133" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M133" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N133" s="6">
+        <v>0</v>
+      </c>
+      <c r="O133" s="6">
+        <v>0</v>
+      </c>
+      <c r="P133" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C134" s="6">
+        <v>10013</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E134" s="6">
+        <v>10014</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G134" s="6">
+        <v>0</v>
+      </c>
+      <c r="H134" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I134" s="6">
+        <v>200801</v>
+      </c>
+      <c r="J134" s="6">
+        <v>0</v>
+      </c>
+      <c r="K134" s="6">
+        <v>0</v>
+      </c>
+      <c r="L134" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M134" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N134" s="6">
+        <v>0</v>
+      </c>
+      <c r="O134" s="6">
+        <v>0</v>
+      </c>
+      <c r="P134" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C135" s="6">
+        <v>10014</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E135" s="6">
+        <v>10015</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G135" s="6">
+        <v>0</v>
+      </c>
+      <c r="H135" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I135" s="6">
+        <v>200901</v>
+      </c>
+      <c r="J135" s="6">
+        <v>0</v>
+      </c>
+      <c r="K135" s="6">
+        <v>0</v>
+      </c>
+      <c r="L135" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M135" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N135" s="6">
+        <v>0</v>
+      </c>
+      <c r="O135" s="6">
+        <v>0</v>
+      </c>
+      <c r="P135" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C136" s="6">
+        <v>10015</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E136" s="6">
+        <v>10016</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G136" s="6">
+        <v>0</v>
+      </c>
+      <c r="H136" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I136" s="6">
+        <v>201001</v>
+      </c>
+      <c r="J136" s="6">
+        <v>0</v>
+      </c>
+      <c r="K136" s="6">
+        <v>0</v>
+      </c>
+      <c r="L136" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M136" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N136" s="6">
+        <v>0</v>
+      </c>
+      <c r="O136" s="6">
+        <v>0</v>
+      </c>
+      <c r="P136" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C137" s="6">
+        <v>10016</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E137" s="6">
+        <v>10017</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G137" s="6">
+        <v>0</v>
+      </c>
+      <c r="H137" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I137" s="6">
+        <v>202201</v>
+      </c>
+      <c r="J137" s="6">
+        <v>0</v>
+      </c>
+      <c r="K137" s="6">
+        <v>0</v>
+      </c>
+      <c r="L137" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M137" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N137" s="6">
+        <v>0</v>
+      </c>
+      <c r="O137" s="6">
+        <v>0</v>
+      </c>
+      <c r="P137" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C138" s="6">
+        <v>10017</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E138" s="6">
+        <v>0</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="G138" s="6">
+        <v>0</v>
+      </c>
+      <c r="H138" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="I138" s="6">
+        <v>202301</v>
+      </c>
+      <c r="J138" s="6">
+        <v>0</v>
+      </c>
+      <c r="K138" s="6">
+        <v>0</v>
+      </c>
+      <c r="L138" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="M138" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="N138" s="6">
+        <v>0</v>
+      </c>
+      <c r="O138" s="6">
+        <v>0</v>
+      </c>
+      <c r="P138" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C139" s="8">
         <v>30001</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="D139" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E122" s="6">
-        <v>0</v>
-      </c>
-      <c r="F122" s="6">
-        <v>0</v>
-      </c>
-      <c r="G122" s="6">
-        <v>0</v>
-      </c>
-      <c r="H122" s="6">
-        <v>1</v>
-      </c>
-      <c r="I122" s="6">
+      <c r="E139" s="6">
+        <v>0</v>
+      </c>
+      <c r="F139" s="6">
+        <v>0</v>
+      </c>
+      <c r="G139" s="6">
+        <v>0</v>
+      </c>
+      <c r="H139" s="6">
+        <v>1</v>
+      </c>
+      <c r="I139" s="6">
         <v>100403</v>
       </c>
-      <c r="J122" s="6">
-        <v>0</v>
-      </c>
-      <c r="K122" s="6">
-        <v>1</v>
-      </c>
-      <c r="L122" s="6">
-        <v>1</v>
-      </c>
-      <c r="M122" s="6">
+      <c r="J139" s="6">
+        <v>0</v>
+      </c>
+      <c r="K139" s="6">
+        <v>1</v>
+      </c>
+      <c r="L139" s="6">
+        <v>1</v>
+      </c>
+      <c r="M139" s="6">
         <v>40</v>
       </c>
-      <c r="N122" s="6">
-        <v>0</v>
-      </c>
-      <c r="O122" s="6">
-        <v>0</v>
-      </c>
-      <c r="P122" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.15">
-      <c r="C123" s="8">
+      <c r="N139" s="6">
+        <v>0</v>
+      </c>
+      <c r="O139" s="6">
+        <v>0</v>
+      </c>
+      <c r="P139" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C140" s="8">
         <v>40001</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="D140" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E123" s="6">
-        <v>0</v>
-      </c>
-      <c r="F123" s="6">
-        <v>0</v>
-      </c>
-      <c r="G123" s="6">
-        <v>0</v>
-      </c>
-      <c r="H123" s="6">
-        <v>1</v>
-      </c>
-      <c r="I123" s="6">
+      <c r="E140" s="6">
+        <v>0</v>
+      </c>
+      <c r="F140" s="6">
+        <v>0</v>
+      </c>
+      <c r="G140" s="6">
+        <v>0</v>
+      </c>
+      <c r="H140" s="6">
+        <v>1</v>
+      </c>
+      <c r="I140" s="6">
         <v>68000104</v>
       </c>
-      <c r="J123" s="6">
-        <v>0</v>
-      </c>
-      <c r="K123" s="6">
-        <v>0</v>
-      </c>
-      <c r="L123" s="6">
-        <v>0</v>
-      </c>
-      <c r="M123" s="6">
-        <v>0</v>
-      </c>
-      <c r="N123" s="6">
-        <v>0</v>
-      </c>
-      <c r="O123" s="6">
-        <v>1</v>
-      </c>
-      <c r="P123" s="6">
+      <c r="J140" s="6">
+        <v>0</v>
+      </c>
+      <c r="K140" s="6">
+        <v>0</v>
+      </c>
+      <c r="L140" s="6">
+        <v>0</v>
+      </c>
+      <c r="M140" s="6">
+        <v>0</v>
+      </c>
+      <c r="N140" s="6">
+        <v>0</v>
+      </c>
+      <c r="O140" s="6">
+        <v>1</v>
+      </c>
+      <c r="P140" s="6">
         <v>3</v>
       </c>
     </row>
+    <row r="141" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/HideProListConfig.xlsx
+++ b/Excel/HideProListConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D39CC7-340F-439E-8CF7-59038C58C6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893CC55C-9DC5-428F-82B1-B4B5353D517C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,13 +403,7 @@
     <t>PropertyType</t>
   </si>
   <si>
-    <t>IfEquipLvUp</t>
-  </si>
-  <si>
     <t>HideProValueType</t>
-  </si>
-  <si>
-    <t>PropertyValueMin</t>
   </si>
   <si>
     <t>PropertyValueMax</t>
@@ -707,6 +701,14 @@
   </si>
   <si>
     <t>3001,3002,3003</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyValueMin</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>IfEquipLvUp</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -2652,10 +2654,10 @@
         <v>10</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2681,83 +2683,83 @@
         <v>16</v>
       </c>
       <c r="J4" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="O4" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="6">
         <v>1001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E6" s="6">
         <v>1002</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
@@ -2790,18 +2792,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="6">
         <v>1002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" s="6">
         <v>1003</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7" s="6">
         <v>0</v>
@@ -2834,18 +2836,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="6">
         <v>1003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E8" s="6">
         <v>1004</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G8" s="6">
         <v>0</v>
@@ -2878,18 +2880,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="6">
         <v>1004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9" s="6">
         <v>1005</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G9" s="6">
         <v>0</v>
@@ -2922,18 +2924,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="6">
         <v>1005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" s="6">
         <v>1006</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G10" s="6">
         <v>0</v>
@@ -2966,18 +2968,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="6">
         <v>1006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" s="6">
         <v>1007</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G11" s="6">
         <v>0</v>
@@ -3010,18 +3012,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="6">
         <v>1007</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6">
         <v>1008</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G12" s="6">
         <v>0</v>
@@ -3054,18 +3056,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="6">
         <v>1008</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" s="6">
         <v>1009</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" s="6">
         <v>0</v>
@@ -3098,18 +3100,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="6">
         <v>1009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E14" s="6">
         <v>1010</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G14" s="6">
         <v>0</v>
@@ -3142,18 +3144,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="6">
         <v>1010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" s="6">
         <v>1011</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G15" s="6">
         <v>0</v>
@@ -3186,18 +3188,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="6">
         <v>1011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E16" s="6">
         <v>1012</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G16" s="6">
         <v>0</v>
@@ -3230,18 +3232,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="6">
         <v>1012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E17" s="6">
         <v>1013</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G17" s="6">
         <v>0</v>
@@ -3274,18 +3276,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="6">
         <v>1013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E18" s="6">
         <v>1014</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G18" s="6">
         <v>0</v>
@@ -3318,18 +3320,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="6">
         <v>1014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E19" s="6">
         <v>1015</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G19" s="6">
         <v>0</v>
@@ -3362,18 +3364,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="6">
         <v>1015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E20" s="6">
         <v>1016</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G20" s="6">
         <v>0</v>
@@ -3406,18 +3408,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="6">
         <v>1016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E21" s="6">
         <v>1017</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G21" s="6">
         <v>0</v>
@@ -3450,18 +3452,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="6">
         <v>1017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E22" s="6">
         <v>1018</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G22" s="6">
         <v>0</v>
@@ -3494,18 +3496,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="6">
         <v>1018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E23" s="6">
         <v>1019</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G23" s="6">
         <v>0</v>
@@ -3538,18 +3540,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="6">
         <v>1019</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E24" s="6">
         <v>1020</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G24" s="6">
         <v>0</v>
@@ -3582,18 +3584,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="6">
         <v>1020</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E25" s="6">
         <v>1021</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G25" s="6">
         <v>0</v>
@@ -3626,18 +3628,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="6">
         <v>1021</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E26" s="6">
         <v>1022</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G26" s="6">
         <v>0</v>
@@ -3670,18 +3672,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="6">
         <v>1022</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E27" s="6">
         <v>1023</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G27" s="6">
         <v>0</v>
@@ -3714,18 +3716,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="6">
         <v>1023</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E28" s="6">
         <v>1024</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G28" s="6">
         <v>0</v>
@@ -3758,18 +3760,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="6">
         <v>1024</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E29" s="6">
         <v>1025</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G29" s="6">
         <v>0</v>
@@ -3802,18 +3804,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="6">
         <v>1025</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E30" s="6">
         <v>1026</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G30" s="6">
         <v>0</v>
@@ -3846,18 +3848,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="6">
         <v>1026</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E31" s="6">
         <v>1027</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G31" s="6">
         <v>0</v>
@@ -3890,18 +3892,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="6">
         <v>1027</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" s="6">
         <v>1028</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G32" s="6">
         <v>0</v>
@@ -3934,18 +3936,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="6">
         <v>1028</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E33" s="6">
         <v>1030</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G33" s="6">
         <v>0</v>
@@ -3978,18 +3980,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="6">
         <v>1030</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E34" s="6">
         <v>1031</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G34" s="6">
         <v>0</v>
@@ -4022,18 +4024,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="6">
         <v>1031</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E35" s="6">
         <v>1032</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G35" s="6">
         <v>0</v>
@@ -4066,18 +4068,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="6">
         <v>1032</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E36" s="6">
         <v>1033</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G36" s="6">
         <v>0</v>
@@ -4110,18 +4112,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="6">
         <v>1033</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E37" s="6">
         <v>1034</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G37" s="6">
         <v>0</v>
@@ -4154,18 +4156,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="6">
         <v>1034</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E38" s="6">
         <v>1035</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G38" s="6">
         <v>0</v>
@@ -4198,18 +4200,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="6">
         <v>1035</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E39" s="6">
         <v>1036</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G39" s="6">
         <v>0</v>
@@ -4242,18 +4244,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="6">
         <v>1036</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E40" s="6">
         <v>1037</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G40" s="6">
         <v>0</v>
@@ -4286,18 +4288,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="6">
         <v>1037</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E41" s="6">
         <v>1038</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G41" s="6">
         <v>0</v>
@@ -4330,18 +4332,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="6">
         <v>1038</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E42" s="6">
         <v>1039</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G42" s="6">
         <v>0</v>
@@ -4374,18 +4376,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="6">
         <v>1039</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E43" s="6">
         <v>1040</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G43" s="6">
         <v>0</v>
@@ -4418,18 +4420,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="6">
         <v>1040</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E44" s="6">
         <v>1041</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G44" s="6">
         <v>0</v>
@@ -4462,18 +4464,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="6">
         <v>1041</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E45" s="6">
         <v>1042</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G45" s="6">
         <v>0</v>
@@ -4506,18 +4508,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="6">
         <v>1042</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E46" s="6">
         <v>1043</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G46" s="6">
         <v>0</v>
@@ -4550,18 +4552,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="6">
         <v>1043</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E47" s="6">
         <v>1044</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G47" s="6">
         <v>0</v>
@@ -4594,18 +4596,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="6">
         <v>1044</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E48" s="6">
         <v>1045</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G48" s="6">
         <v>0</v>
@@ -4638,18 +4640,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="6">
         <v>1045</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E49" s="6">
         <v>1046</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G49" s="6">
         <v>0</v>
@@ -4682,18 +4684,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="6">
         <v>1046</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E50" s="6">
         <v>1047</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G50" s="6">
         <v>0</v>
@@ -4726,18 +4728,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="6">
         <v>1047</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E51" s="6">
         <v>0</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G51" s="6">
         <v>0</v>
@@ -4770,12 +4772,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="6">
         <v>2001</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E52" s="6">
         <v>2002</v>
@@ -4814,18 +4816,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="6">
         <v>2002</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E53" s="6">
         <v>2003</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G53" s="6">
         <v>6</v>
@@ -4858,12 +4860,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="6">
         <v>2003</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E54" s="6">
         <v>2004</v>
@@ -4902,18 +4904,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="6">
         <v>2004</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E55" s="6">
         <v>2005</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G55" s="6">
         <v>1</v>
@@ -4946,18 +4948,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="6">
         <v>2005</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E56" s="6">
         <v>2006</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G56" s="6">
         <v>0</v>
@@ -4990,12 +4992,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="6">
         <v>2006</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E57" s="6">
         <v>2007</v>
@@ -5034,18 +5036,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="6">
         <v>2007</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E58" s="6">
         <v>2008</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G58" s="6">
         <v>2</v>
@@ -5078,18 +5080,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="6">
         <v>2008</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E59" s="6">
         <v>2009</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G59" s="6">
         <v>7</v>
@@ -5122,12 +5124,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="6">
         <v>2009</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E60" s="6">
         <v>2010</v>
@@ -5166,18 +5168,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="6">
         <v>2010</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E61" s="6">
         <v>2011</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G61" s="6">
         <v>0</v>
@@ -5210,18 +5212,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="6">
         <v>2011</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E62" s="6">
         <v>2012</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G62" s="6">
         <v>7</v>
@@ -5254,18 +5256,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="6">
         <v>2012</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E63" s="6">
         <v>2013</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G63" s="6">
         <v>3</v>
@@ -5298,18 +5300,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="6">
         <v>2013</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E64" s="6">
         <v>2014</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G64" s="6">
         <v>4</v>
@@ -5342,18 +5344,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="6">
         <v>2014</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E65" s="6">
         <v>2015</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G65" s="6">
         <v>3</v>
@@ -5386,18 +5388,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="6">
         <v>2015</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E66" s="6">
         <v>2016</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G66" s="6">
         <v>4</v>
@@ -5430,12 +5432,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="6">
         <v>2016</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E67" s="6">
         <v>2017</v>
@@ -5474,18 +5476,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="6">
         <v>2017</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E68" s="6">
         <v>2101</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G68" s="6">
         <v>5</v>
@@ -5518,18 +5520,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="6">
         <v>2101</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E69" s="6">
         <v>2102</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G69" s="6">
         <v>0</v>
@@ -5562,18 +5564,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="6">
         <v>2102</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E70" s="6">
         <v>2103</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G70" s="6">
         <v>1</v>
@@ -5606,18 +5608,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="6">
         <v>2103</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E71" s="6">
         <v>2104</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G71" s="6">
         <v>2</v>
@@ -5650,18 +5652,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="6">
         <v>2104</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E72" s="6">
         <v>2105</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G72" s="6">
         <v>0</v>
@@ -5694,18 +5696,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="6">
         <v>2105</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E73" s="6">
         <v>2106</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G73" s="6">
         <v>0</v>
@@ -5738,18 +5740,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="6">
         <v>2106</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E74" s="6">
         <v>2107</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G74" s="6">
         <v>0</v>
@@ -5782,18 +5784,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="6">
         <v>2107</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E75" s="6">
         <v>2108</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G75" s="6">
         <v>0</v>
@@ -5826,18 +5828,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C76" s="6">
         <v>2108</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E76" s="6">
         <v>2109</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G76" s="6">
         <v>0</v>
@@ -5870,18 +5872,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="6">
         <v>2109</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E77" s="6">
         <v>2110</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G77" s="6">
         <v>0</v>
@@ -5914,18 +5916,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="6">
         <v>2110</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E78" s="6">
         <v>2111</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G78" s="6">
         <v>3</v>
@@ -5958,18 +5960,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="6">
         <v>2111</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E79" s="6">
         <v>2112</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G79" s="6">
         <v>4</v>
@@ -6002,18 +6004,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="6">
         <v>2112</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E80" s="6">
         <v>2113</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G80" s="6">
         <v>5</v>
@@ -6046,18 +6048,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C81" s="6">
         <v>2113</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E81" s="6">
         <v>0</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G81" s="6">
         <v>6</v>
@@ -6090,19 +6092,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="7"/>
       <c r="C82" s="6">
         <v>3101</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E82" s="6">
         <v>0</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G82" s="6">
         <v>0</v>
@@ -6135,19 +6137,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="7"/>
       <c r="C83" s="6">
         <v>3102</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E83" s="6">
         <v>0</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G83" s="6">
         <v>0</v>
@@ -6180,19 +6182,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="7"/>
       <c r="C84" s="6">
         <v>3103</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E84" s="6">
         <v>0</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G84" s="6">
         <v>0</v>
@@ -6225,19 +6227,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="7"/>
       <c r="C85" s="6">
         <v>3104</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E85" s="6">
         <v>0</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G85" s="6">
         <v>0</v>
@@ -6270,19 +6272,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="7"/>
       <c r="C86" s="6">
         <v>3105</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E86" s="6">
         <v>0</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G86" s="6">
         <v>0</v>
@@ -6315,19 +6317,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="7"/>
       <c r="C87" s="6">
         <v>3201</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E87" s="6">
         <v>0</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G87" s="6">
         <v>0</v>
@@ -6360,19 +6362,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="7"/>
       <c r="C88" s="6">
         <v>3202</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E88" s="6">
         <v>0</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G88" s="6">
         <v>0</v>
@@ -6405,19 +6407,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="7"/>
       <c r="C89" s="6">
         <v>3203</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E89" s="6">
         <v>0</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G89" s="6">
         <v>0</v>
@@ -6450,19 +6452,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B90" s="7"/>
       <c r="C90" s="6">
         <v>3204</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E90" s="6">
         <v>0</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G90" s="6">
         <v>0</v>
@@ -6495,19 +6497,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B91" s="7"/>
       <c r="C91" s="6">
         <v>3205</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E91" s="6">
         <v>0</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G91" s="6">
         <v>0</v>
@@ -6540,19 +6542,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B92" s="7"/>
       <c r="C92" s="6">
         <v>3301</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E92" s="6">
         <v>0</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G92" s="6">
         <v>0</v>
@@ -6585,19 +6587,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B93" s="7"/>
       <c r="C93" s="6">
         <v>3302</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E93" s="6">
         <v>0</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G93" s="6">
         <v>0</v>
@@ -6630,19 +6632,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B94" s="7"/>
       <c r="C94" s="6">
         <v>3303</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E94" s="6">
         <v>0</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G94" s="6">
         <v>0</v>
@@ -6675,19 +6677,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B95" s="7"/>
       <c r="C95" s="6">
         <v>3304</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E95" s="6">
         <v>0</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G95" s="6">
         <v>0</v>
@@ -6720,19 +6722,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B96" s="7"/>
       <c r="C96" s="6">
         <v>3305</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E96" s="6">
         <v>0</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G96" s="6">
         <v>0</v>
@@ -6765,19 +6767,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B97" s="7"/>
       <c r="C97" s="6">
         <v>3401</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E97" s="6">
         <v>0</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G97" s="6">
         <v>0</v>
@@ -6810,19 +6812,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B98" s="7"/>
       <c r="C98" s="6">
         <v>3402</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E98" s="6">
         <v>0</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G98" s="6">
         <v>0</v>
@@ -6855,19 +6857,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B99" s="7"/>
       <c r="C99" s="6">
         <v>3403</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E99" s="6">
         <v>0</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G99" s="6">
         <v>0</v>
@@ -6900,19 +6902,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B100" s="7"/>
       <c r="C100" s="6">
         <v>3404</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E100" s="6">
         <v>0</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G100" s="6">
         <v>0</v>
@@ -6945,19 +6947,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B101" s="7"/>
       <c r="C101" s="6">
         <v>3405</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E101" s="6">
         <v>0</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G101" s="6">
         <v>0</v>
@@ -6990,19 +6992,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B102" s="7"/>
       <c r="C102" s="6">
         <v>3501</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E102" s="6">
         <v>0</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G102" s="6">
         <v>0</v>
@@ -7035,19 +7037,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B103" s="7"/>
       <c r="C103" s="6">
         <v>3502</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E103" s="6">
         <v>0</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G103" s="6">
         <v>0</v>
@@ -7080,19 +7082,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B104" s="7"/>
       <c r="C104" s="6">
         <v>3503</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E104" s="6">
         <v>0</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G104" s="6">
         <v>0</v>
@@ -7125,19 +7127,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B105" s="7"/>
       <c r="C105" s="6">
         <v>3504</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E105" s="6">
         <v>0</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G105" s="6">
         <v>0</v>
@@ -7170,19 +7172,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B106" s="7"/>
       <c r="C106" s="6">
         <v>3505</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E106" s="6">
         <v>0</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G106" s="6">
         <v>0</v>
@@ -7215,19 +7217,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B107" s="7"/>
       <c r="C107" s="6">
         <v>3601</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E107" s="6">
         <v>0</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G107" s="6">
         <v>0</v>
@@ -7260,19 +7262,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B108" s="7"/>
       <c r="C108" s="6">
         <v>3602</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E108" s="6">
         <v>0</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G108" s="6">
         <v>0</v>
@@ -7305,19 +7307,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B109" s="7"/>
       <c r="C109" s="6">
         <v>3603</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E109" s="6">
         <v>0</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G109" s="6">
         <v>0</v>
@@ -7350,19 +7352,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B110" s="7"/>
       <c r="C110" s="6">
         <v>3604</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E110" s="6">
         <v>0</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G110" s="6">
         <v>0</v>
@@ -7395,19 +7397,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B111" s="7"/>
       <c r="C111" s="6">
         <v>3605</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E111" s="6">
         <v>0</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G111" s="6">
         <v>0</v>
@@ -7440,18 +7442,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C112" s="6">
         <v>3901</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E112" s="6">
         <v>1013</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G112" s="6">
         <v>0</v>
@@ -7484,18 +7486,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C113" s="6">
         <v>3902</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E113" s="6">
         <v>2109</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G113" s="6">
         <v>0</v>
@@ -7528,18 +7530,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="6">
         <v>3903</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E114" s="6">
         <v>2105</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G114" s="6">
         <v>0</v>
@@ -7572,18 +7574,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="6">
         <v>3904</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E115" s="6">
         <v>2106</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G115" s="6">
         <v>0</v>
@@ -7616,19 +7618,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B116" s="7"/>
       <c r="C116" s="6">
         <v>3905</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E116" s="6">
         <v>0</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G116" s="6">
         <v>0</v>
@@ -7661,18 +7663,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="6">
         <v>3906</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E117" s="6">
         <v>1018</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G117" s="6">
         <v>0</v>
@@ -7705,18 +7707,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="6">
         <v>3907</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E118" s="6">
         <v>1019</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G118" s="6">
         <v>0</v>
@@ -7749,18 +7751,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C119" s="6">
         <v>3908</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E119" s="6">
         <v>1020</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G119" s="6">
         <v>0</v>
@@ -7793,18 +7795,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C120" s="6">
         <v>3909</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E120" s="6">
         <v>1021</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G120" s="6">
         <v>0</v>
@@ -7837,18 +7839,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C121" s="6">
         <v>3910</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E121" s="6">
         <v>1008</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G121" s="6">
         <v>0</v>
@@ -7886,13 +7888,13 @@
         <v>10001</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E122" s="6">
         <v>10002</v>
       </c>
       <c r="F122" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G122" s="6">
         <v>0</v>
@@ -7930,13 +7932,13 @@
         <v>10002</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E123" s="6">
         <v>10003</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G123" s="6">
         <v>0</v>
@@ -7974,13 +7976,13 @@
         <v>10003</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E124" s="6">
         <v>10004</v>
       </c>
       <c r="F124" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G124" s="6">
         <v>0</v>
@@ -8018,13 +8020,13 @@
         <v>10004</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E125" s="6">
         <v>10005</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G125" s="6">
         <v>0</v>
@@ -8062,13 +8064,13 @@
         <v>10005</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E126" s="6">
         <v>10006</v>
       </c>
       <c r="F126" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G126" s="6">
         <v>0</v>
@@ -8080,16 +8082,16 @@
         <v>200101</v>
       </c>
       <c r="J126" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K126" s="6">
         <v>0</v>
       </c>
       <c r="L126" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M126" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M126" s="6">
-        <v>0.05</v>
       </c>
       <c r="N126" s="6">
         <v>0</v>
@@ -8106,13 +8108,13 @@
         <v>10006</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E127" s="6">
         <v>10007</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G127" s="6">
         <v>0</v>
@@ -8124,16 +8126,16 @@
         <v>200201</v>
       </c>
       <c r="J127" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" s="6">
         <v>0</v>
       </c>
       <c r="L127" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M127" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M127" s="6">
-        <v>0.05</v>
       </c>
       <c r="N127" s="6">
         <v>0</v>
@@ -8150,13 +8152,13 @@
         <v>10007</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E128" s="6">
         <v>10008</v>
       </c>
       <c r="F128" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G128" s="6">
         <v>0</v>
@@ -8168,16 +8170,16 @@
         <v>200301</v>
       </c>
       <c r="J128" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" s="6">
         <v>0</v>
       </c>
       <c r="L128" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M128" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M128" s="6">
-        <v>0.05</v>
       </c>
       <c r="N128" s="6">
         <v>0</v>
@@ -8194,13 +8196,13 @@
         <v>10008</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E129" s="6">
         <v>10009</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G129" s="6">
         <v>0</v>
@@ -8212,16 +8214,16 @@
         <v>200401</v>
       </c>
       <c r="J129" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" s="6">
         <v>0</v>
       </c>
       <c r="L129" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M129" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M129" s="6">
-        <v>0.05</v>
       </c>
       <c r="N129" s="6">
         <v>0</v>
@@ -8238,13 +8240,13 @@
         <v>10009</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E130" s="6">
         <v>10010</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G130" s="6">
         <v>0</v>
@@ -8256,16 +8258,16 @@
         <v>202101</v>
       </c>
       <c r="J130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" s="6">
         <v>0</v>
       </c>
       <c r="L130" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M130" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M130" s="6">
-        <v>0.05</v>
       </c>
       <c r="N130" s="6">
         <v>0</v>
@@ -8282,13 +8284,13 @@
         <v>10010</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E131" s="6">
         <v>10011</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G131" s="6">
         <v>0</v>
@@ -8300,16 +8302,16 @@
         <v>200501</v>
       </c>
       <c r="J131" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" s="6">
         <v>0</v>
       </c>
       <c r="L131" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M131" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M131" s="6">
-        <v>0.05</v>
       </c>
       <c r="N131" s="6">
         <v>0</v>
@@ -8326,13 +8328,13 @@
         <v>10011</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E132" s="6">
         <v>10012</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G132" s="6">
         <v>0</v>
@@ -8344,16 +8346,16 @@
         <v>200601</v>
       </c>
       <c r="J132" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" s="6">
         <v>0</v>
       </c>
       <c r="L132" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M132" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M132" s="6">
-        <v>0.05</v>
       </c>
       <c r="N132" s="6">
         <v>0</v>
@@ -8370,13 +8372,13 @@
         <v>10012</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E133" s="6">
         <v>10013</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G133" s="6">
         <v>0</v>
@@ -8388,16 +8390,16 @@
         <v>200701</v>
       </c>
       <c r="J133" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" s="6">
         <v>0</v>
       </c>
       <c r="L133" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M133" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M133" s="6">
-        <v>0.05</v>
       </c>
       <c r="N133" s="6">
         <v>0</v>
@@ -8414,13 +8416,13 @@
         <v>10013</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E134" s="6">
         <v>10014</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G134" s="6">
         <v>0</v>
@@ -8432,16 +8434,16 @@
         <v>200801</v>
       </c>
       <c r="J134" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" s="6">
         <v>0</v>
       </c>
       <c r="L134" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M134" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M134" s="6">
-        <v>0.05</v>
       </c>
       <c r="N134" s="6">
         <v>0</v>
@@ -8458,13 +8460,13 @@
         <v>10014</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E135" s="6">
         <v>10015</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G135" s="6">
         <v>0</v>
@@ -8476,16 +8478,16 @@
         <v>200901</v>
       </c>
       <c r="J135" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K135" s="6">
         <v>0</v>
       </c>
       <c r="L135" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M135" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M135" s="6">
-        <v>0.05</v>
       </c>
       <c r="N135" s="6">
         <v>0</v>
@@ -8502,13 +8504,13 @@
         <v>10015</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E136" s="6">
         <v>10016</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G136" s="6">
         <v>0</v>
@@ -8520,16 +8522,16 @@
         <v>201001</v>
       </c>
       <c r="J136" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" s="6">
         <v>0</v>
       </c>
       <c r="L136" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M136" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M136" s="6">
-        <v>0.05</v>
       </c>
       <c r="N136" s="6">
         <v>0</v>
@@ -8546,13 +8548,13 @@
         <v>10016</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E137" s="6">
         <v>10017</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G137" s="6">
         <v>0</v>
@@ -8564,16 +8566,16 @@
         <v>202201</v>
       </c>
       <c r="J137" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" s="6">
         <v>0</v>
       </c>
       <c r="L137" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M137" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M137" s="6">
-        <v>0.05</v>
       </c>
       <c r="N137" s="6">
         <v>0</v>
@@ -8590,13 +8592,13 @@
         <v>10017</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E138" s="6">
         <v>0</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G138" s="6">
         <v>0</v>
@@ -8608,16 +8610,16 @@
         <v>202301</v>
       </c>
       <c r="J138" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" s="6">
         <v>0</v>
       </c>
       <c r="L138" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="M138" s="6">
         <v>0.01</v>
-      </c>
-      <c r="M138" s="6">
-        <v>0.05</v>
       </c>
       <c r="N138" s="6">
         <v>0</v>
@@ -8634,7 +8636,7 @@
         <v>30001</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E139" s="6">
         <v>0</v>
@@ -8678,7 +8680,7 @@
         <v>40001</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E140" s="6">
         <v>0</v>

--- a/Excel/HideProListConfig.xlsx
+++ b/Excel/HideProListConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893CC55C-9DC5-428F-82B1-B4B5353D517C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47699BD2-6310-4781-94E9-5BB5F4DB739C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2748,7 +2748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="6">
         <v>1001</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="6">
         <v>1002</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="6">
         <v>1003</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="6">
         <v>1004</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="6">
         <v>1005</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="6">
         <v>1006</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="6">
         <v>1007</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="6">
         <v>1008</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="6">
         <v>1009</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="6">
         <v>1010</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="6">
         <v>1011</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="6">
         <v>1012</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="6">
         <v>1013</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="6">
         <v>1014</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="6">
         <v>1015</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="6">
         <v>1016</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="6">
         <v>1017</v>
       </c>
@@ -3496,7 +3496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="6">
         <v>1018</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="6">
         <v>1019</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="6">
         <v>1020</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="6">
         <v>1021</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="6">
         <v>1022</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="6">
         <v>1023</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="6">
         <v>1024</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="6">
         <v>1025</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="6">
         <v>1026</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="6">
         <v>1027</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="6">
         <v>1028</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="6">
         <v>1030</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="6">
         <v>1031</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="6">
         <v>1032</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="6">
         <v>1033</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="6">
         <v>1034</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="6">
         <v>1035</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="6">
         <v>1036</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>1</v>
       </c>
       <c r="M40" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40" s="6">
         <v>0</v>
@@ -4288,7 +4288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="6">
         <v>1037</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>1</v>
       </c>
       <c r="M41" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N41" s="6">
         <v>0</v>
@@ -4332,7 +4332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="6">
         <v>1038</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>1</v>
       </c>
       <c r="M42" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N42" s="6">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="6">
         <v>1039</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N43" s="6">
         <v>0</v>
@@ -4420,7 +4420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="6">
         <v>1040</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>1</v>
       </c>
       <c r="M44" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N44" s="6">
         <v>0</v>
@@ -4464,7 +4464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="6">
         <v>1041</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="6">
         <v>1042</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="6">
         <v>1043</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="6">
         <v>1044</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="6">
         <v>1045</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="6">
         <v>1046</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="6">
         <v>1047</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="6">
         <v>2001</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="6">
         <v>2002</v>
       </c>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="6">
         <v>2003</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="6">
         <v>2004</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="6">
         <v>2005</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="6">
         <v>2006</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="6">
         <v>2007</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="6">
         <v>2008</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="6">
         <v>2009</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="6">
         <v>2010</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="6">
         <v>2011</v>
       </c>
@@ -5256,7 +5256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="6">
         <v>2012</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="6">
         <v>2013</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="6">
         <v>2014</v>
       </c>
@@ -5388,7 +5388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="6">
         <v>2015</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="6">
         <v>2016</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="6">
         <v>2017</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="6">
         <v>2101</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="6">
         <v>2102</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="6">
         <v>2103</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="6">
         <v>2104</v>
       </c>
@@ -5696,7 +5696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="6">
         <v>2105</v>
       </c>
@@ -5740,7 +5740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="6">
         <v>2106</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="6">
         <v>2107</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C76" s="6">
         <v>2108</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="6">
         <v>2109</v>
       </c>
@@ -5916,7 +5916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="6">
         <v>2110</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="6">
         <v>2111</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="3:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="6">
         <v>2112</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C81" s="6">
         <v>2113</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="7"/>
       <c r="C82" s="6">
         <v>3101</v>
@@ -6137,7 +6137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="7"/>
       <c r="C83" s="6">
         <v>3102</v>
@@ -6182,7 +6182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="7"/>
       <c r="C84" s="6">
         <v>3103</v>
@@ -6227,7 +6227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="7"/>
       <c r="C85" s="6">
         <v>3104</v>
@@ -6272,7 +6272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="7"/>
       <c r="C86" s="6">
         <v>3105</v>
@@ -6317,7 +6317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="7"/>
       <c r="C87" s="6">
         <v>3201</v>
@@ -6362,7 +6362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="7"/>
       <c r="C88" s="6">
         <v>3202</v>
@@ -6407,7 +6407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="7"/>
       <c r="C89" s="6">
         <v>3203</v>
@@ -6452,7 +6452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B90" s="7"/>
       <c r="C90" s="6">
         <v>3204</v>
@@ -6497,7 +6497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B91" s="7"/>
       <c r="C91" s="6">
         <v>3205</v>
@@ -6542,7 +6542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B92" s="7"/>
       <c r="C92" s="6">
         <v>3301</v>
@@ -6587,7 +6587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B93" s="7"/>
       <c r="C93" s="6">
         <v>3302</v>
@@ -6632,7 +6632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B94" s="7"/>
       <c r="C94" s="6">
         <v>3303</v>
@@ -6677,7 +6677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B95" s="7"/>
       <c r="C95" s="6">
         <v>3304</v>
@@ -6722,7 +6722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B96" s="7"/>
       <c r="C96" s="6">
         <v>3305</v>
@@ -6767,7 +6767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B97" s="7"/>
       <c r="C97" s="6">
         <v>3401</v>
@@ -6812,7 +6812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B98" s="7"/>
       <c r="C98" s="6">
         <v>3402</v>
@@ -6857,7 +6857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B99" s="7"/>
       <c r="C99" s="6">
         <v>3403</v>
@@ -6902,7 +6902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B100" s="7"/>
       <c r="C100" s="6">
         <v>3404</v>
@@ -6947,7 +6947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B101" s="7"/>
       <c r="C101" s="6">
         <v>3405</v>
@@ -6992,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B102" s="7"/>
       <c r="C102" s="6">
         <v>3501</v>
@@ -7037,7 +7037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B103" s="7"/>
       <c r="C103" s="6">
         <v>3502</v>
@@ -7082,7 +7082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B104" s="7"/>
       <c r="C104" s="6">
         <v>3503</v>
@@ -7127,7 +7127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B105" s="7"/>
       <c r="C105" s="6">
         <v>3504</v>
@@ -7172,7 +7172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B106" s="7"/>
       <c r="C106" s="6">
         <v>3505</v>
@@ -7217,7 +7217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B107" s="7"/>
       <c r="C107" s="6">
         <v>3601</v>
@@ -7262,7 +7262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B108" s="7"/>
       <c r="C108" s="6">
         <v>3602</v>
@@ -7307,7 +7307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B109" s="7"/>
       <c r="C109" s="6">
         <v>3603</v>
@@ -7352,7 +7352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B110" s="7"/>
       <c r="C110" s="6">
         <v>3604</v>
@@ -7397,7 +7397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B111" s="7"/>
       <c r="C111" s="6">
         <v>3605</v>
@@ -7442,7 +7442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C112" s="6">
         <v>3901</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C113" s="6">
         <v>3902</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="6">
         <v>3903</v>
       </c>
@@ -7574,7 +7574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="6">
         <v>3904</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B116" s="7"/>
       <c r="C116" s="6">
         <v>3905</v>
@@ -7663,7 +7663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="6">
         <v>3906</v>
       </c>
@@ -7707,7 +7707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="6">
         <v>3907</v>
       </c>
@@ -7751,7 +7751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C119" s="6">
         <v>3908</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="2:16" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C120" s="6">
         <v>3909</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C121" s="6">
         <v>3910</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>1</v>
       </c>
       <c r="M139" s="6">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="N139" s="6">
         <v>0</v>

--- a/Excel/HideProListConfig.xlsx
+++ b/Excel/HideProListConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47699BD2-6310-4781-94E9-5BB5F4DB739C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78DB962-BE2F-44C8-8CC2-52EB1051B58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/HideProListConfig.xlsx
+++ b/Excel/HideProListConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78DB962-BE2F-44C8-8CC2-52EB1051B58E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B1DA17-1651-4059-AD16-2C1D937F844C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -203,7 +203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -236,7 +236,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -293,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{5387E174-4222-4CCB-9000-D97FE0608FBD}">
+    <comment ref="P3" authorId="1" shapeId="0" xr:uid="{5387E174-4222-4CCB-9000-D97FE0608FBD}">
       <text>
         <r>
           <rPr>
@@ -320,7 +320,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{94D12ACB-280D-4514-BDFF-1B24A2F737B8}">
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{94D12ACB-280D-4514-BDFF-1B24A2F737B8}">
       <text>
         <r>
           <rPr>
@@ -350,7 +350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="196">
   <si>
     <t>Id</t>
   </si>
@@ -709,6 +709,251 @@
   </si>
   <si>
     <t>IfEquipLvUp</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Life</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Physical defense</t>
+  </si>
+  <si>
+    <t>Magic defense</t>
+  </si>
+  <si>
+    <t>Block Value</t>
+  </si>
+  <si>
+    <t>Heavy Strike Additional Damage</t>
+  </si>
+  <si>
+    <t>Critical hit probability</t>
+  </si>
+  <si>
+    <t>True Damage</t>
+  </si>
+  <si>
+    <t>Recovery Value</t>
+  </si>
+  <si>
+    <t>Ignore the target's defense value.</t>
+  </si>
+  <si>
+    <t>Ignore the target's magic defense value</t>
+  </si>
+  <si>
+    <t>Lucky Value</t>
+  </si>
+  <si>
+    <t>Critical Strike Rating</t>
+  </si>
+  <si>
+    <t>Hit level</t>
+  </si>
+  <si>
+    <t>Dodge Level</t>
+  </si>
+  <si>
+    <t>Resistance to Aggression Level</t>
+  </si>
+  <si>
+    <t>Critical Hit Probability</t>
+  </si>
+  <si>
+    <t>Hit Chance</t>
+  </si>
+  <si>
+    <t>Evasion probability</t>
+  </si>
+  <si>
+    <t>Resistance to Damage Probability</t>
+  </si>
+  <si>
+    <t>Physical damage</t>
+  </si>
+  <si>
+    <t>Magic damage</t>
+  </si>
+  <si>
+    <t>Physical Resistance</t>
+  </si>
+  <si>
+    <t>Magic Resistance</t>
+  </si>
+  <si>
+    <t>Damage Bonus</t>
+  </si>
+  <si>
+    <t>Damage Reduction</t>
+  </si>
+  <si>
+    <t>Attack penetration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Penetration  </t>
+  </si>
+  <si>
+    <t>Physical damage attack on the leader</t>
+  </si>
+  <si>
+    <t>Magical Damage to Lord in Attack</t>
+  </si>
+  <si>
+    <t>Lord's Physical Attack Reduction</t>
+  </si>
+  <si>
+    <t>Lord's magic attack reduction</t>
+  </si>
+  <si>
+    <t>Skill cooldown reduction</t>
+  </si>
+  <si>
+    <t>Experience bonus</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Intelligence</t>
+  </si>
+  <si>
+    <t>Physique</t>
+  </si>
+  <si>
+    <t>Endurance</t>
+  </si>
+  <si>
+    <t>Agile</t>
+  </si>
+  <si>
+    <t>Attack with Sword Weapons</t>
+  </si>
+  <si>
+    <t>Attack with sword-type weapons</t>
+  </si>
+  <si>
+    <t>Staff Weapon Attack</t>
+  </si>
+  <si>
+    <t>Magic Book Weapon Attack</t>
+  </si>
+  <si>
+    <t>Additional Restoration</t>
+  </si>
+  <si>
+    <t>Daze resistance</t>
+  </si>
+  <si>
+    <t>Bow and Arrow Weapon Attack</t>
+  </si>
+  <si>
+    <t>Bravery</t>
+  </si>
+  <si>
+    <t>Angel Resurrection</t>
+  </si>
+  <si>
+    <t>Sputtering</t>
+  </si>
+  <si>
+    <t>Assist in battle</t>
+  </si>
+  <si>
+    <t>Unbreakable Body</t>
+  </si>
+  <si>
+    <t>Penetrating Damage</t>
+  </si>
+  <si>
+    <t>Slowly</t>
+  </si>
+  <si>
+    <t>Swift</t>
+  </si>
+  <si>
+    <t>100% accuracy</t>
+  </si>
+  <si>
+    <t>Mental Concentration</t>
+  </si>
+  <si>
+    <t>Strive</t>
+  </si>
+  <si>
+    <t>Gleaming</t>
+  </si>
+  <si>
+    <t>Invisibility</t>
+  </si>
+  <si>
+    <t>Ignore target</t>
+  </si>
+  <si>
+    <t>Greed</t>
+  </si>
+  <si>
+    <t>Resolution</t>
+  </si>
+  <si>
+    <t>Sprint</t>
+  </si>
+  <si>
+    <t>Shennong</t>
+  </si>
+  <si>
+    <t>Treasure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple  </t>
+  </si>
+  <si>
+    <t>Gourmet</t>
+  </si>
+  <si>
+    <t>Chance of winning</t>
+  </si>
+  <si>
+    <t>No level</t>
+  </si>
+  <si>
+    <t>Weakness</t>
+  </si>
+  <si>
+    <t>Gem specialization</t>
+  </si>
+  <si>
+    <t>Healing during battles</t>
+  </si>
+  <si>
+    <t>The Hand of Attack</t>
+  </si>
+  <si>
+    <t>Hand of Defense</t>
+  </si>
+  <si>
+    <t>Resting Hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Defense</t>
+  </si>
+  <si>
+    <t>Magic Defense</t>
+  </si>
+  <si>
+    <t>Skill damage</t>
+  </si>
+  <si>
+    <t>Rare pet</t>
+  </si>
+  <si>
+    <t>Name_EN</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1927,7 +2172,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1953,6 +2198,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="313">
@@ -2599,24 +2847,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:P145"/>
+  <dimension ref="B1:Q145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="11.375" customWidth="1"/>
-    <col min="4" max="4" width="18.875" customWidth="1"/>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="7" width="22.875" customWidth="1"/>
-    <col min="8" max="8" width="11.375" customWidth="1"/>
-    <col min="9" max="9" width="12.75" customWidth="1"/>
-    <col min="10" max="11" width="15" customWidth="1"/>
-    <col min="12" max="13" width="17.125" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="16" width="13.25" customWidth="1"/>
+    <col min="4" max="5" width="18.875" customWidth="1"/>
+    <col min="6" max="6" width="11.875" customWidth="1"/>
+    <col min="7" max="8" width="22.875" customWidth="1"/>
+    <col min="9" max="9" width="11.375" customWidth="1"/>
+    <col min="10" max="10" width="12.75" customWidth="1"/>
+    <col min="11" max="12" width="15" customWidth="1"/>
+    <col min="13" max="14" width="17.125" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="17" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="2" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="3" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="2" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E2" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -2624,43 +2876,46 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C4" s="4" t="s">
         <v>0</v>
       </c>
@@ -2668,43 +2923,46 @@
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="J4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="L4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="M4" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="N4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="O4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="P4" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="Q4" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
@@ -2712,19 +2970,19 @@
         <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>20</v>
@@ -2733,13 +2991,13 @@
         <v>20</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>20</v>
@@ -2747,208 +3005,223 @@
       <c r="P5" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="6">
         <v>1001</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="6">
         <v>1002</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
+      <c r="G6" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
         <v>0.02</v>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6">
         <v>100202</v>
       </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
       <c r="K6" s="6">
         <v>0</v>
       </c>
       <c r="L6" s="6">
+        <v>0</v>
+      </c>
+      <c r="M6" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M6" s="6">
+      <c r="N6" s="6">
         <v>0.02</v>
       </c>
-      <c r="N6" s="6">
-        <v>0</v>
-      </c>
       <c r="O6" s="6">
         <v>0</v>
       </c>
       <c r="P6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="6">
         <v>1002</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" s="6">
         <v>1003</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
+      <c r="G7" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
         <v>0.02</v>
       </c>
-      <c r="I7" s="6">
+      <c r="J7" s="6">
         <v>100402</v>
       </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
       <c r="K7" s="6">
         <v>0</v>
       </c>
       <c r="L7" s="6">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M7" s="6">
+      <c r="N7" s="6">
         <v>0.02</v>
       </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
       <c r="O7" s="6">
         <v>0</v>
       </c>
       <c r="P7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="6">
         <v>1003</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="6">
         <v>1004</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
+      <c r="G8" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
         <v>0.02</v>
       </c>
-      <c r="I8" s="6">
+      <c r="J8" s="6">
         <v>100602</v>
       </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
       <c r="K8" s="6">
         <v>0</v>
       </c>
       <c r="L8" s="6">
+        <v>0</v>
+      </c>
+      <c r="M8" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M8" s="6">
+      <c r="N8" s="6">
         <v>0.02</v>
       </c>
-      <c r="N8" s="6">
-        <v>0</v>
-      </c>
       <c r="O8" s="6">
         <v>0</v>
       </c>
       <c r="P8" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C9" s="6">
         <v>1004</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="6">
         <v>1005</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
+      <c r="G9" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
         <v>0.02</v>
       </c>
-      <c r="I9" s="6">
+      <c r="J9" s="6">
         <v>100802</v>
       </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
       <c r="K9" s="6">
         <v>0</v>
       </c>
       <c r="L9" s="6">
+        <v>0</v>
+      </c>
+      <c r="M9" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M9" s="6">
+      <c r="N9" s="6">
         <v>0.02</v>
       </c>
-      <c r="N9" s="6">
-        <v>0</v>
-      </c>
       <c r="O9" s="6">
         <v>0</v>
       </c>
       <c r="P9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C10" s="6">
         <v>1005</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="6">
         <v>1006</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0</v>
+      <c r="G10" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
         <v>0.03</v>
       </c>
-      <c r="I10" s="6">
+      <c r="J10" s="6">
         <v>110101</v>
       </c>
-      <c r="J10" s="6">
-        <v>1</v>
-      </c>
       <c r="K10" s="6">
         <v>1</v>
       </c>
@@ -2956,131 +3229,140 @@
         <v>1</v>
       </c>
       <c r="M10" s="6">
+        <v>1</v>
+      </c>
+      <c r="N10" s="6">
         <v>10</v>
       </c>
-      <c r="N10" s="6">
-        <v>0</v>
-      </c>
       <c r="O10" s="6">
         <v>0</v>
       </c>
       <c r="P10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C11" s="6">
         <v>1006</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" s="6">
         <v>1007</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
+      <c r="G11" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
         <v>0.03</v>
       </c>
-      <c r="I11" s="6">
+      <c r="J11" s="6">
         <v>110201</v>
       </c>
-      <c r="J11" s="6">
-        <v>1</v>
-      </c>
       <c r="K11" s="6">
         <v>1</v>
       </c>
       <c r="L11" s="6">
+        <v>1</v>
+      </c>
+      <c r="M11" s="6">
         <v>10</v>
       </c>
-      <c r="M11" s="6">
+      <c r="N11" s="6">
         <v>30</v>
       </c>
-      <c r="N11" s="6">
-        <v>0</v>
-      </c>
       <c r="O11" s="6">
         <v>0</v>
       </c>
       <c r="P11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C12" s="6">
         <v>1007</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="6">
         <v>1008</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
+      <c r="G12" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
         <v>0.03</v>
       </c>
-      <c r="I12" s="6">
+      <c r="J12" s="6">
         <v>202101</v>
       </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
       <c r="K12" s="6">
         <v>0</v>
       </c>
       <c r="L12" s="6">
+        <v>0</v>
+      </c>
+      <c r="M12" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M12" s="6">
+      <c r="N12" s="6">
         <v>0.02</v>
       </c>
-      <c r="N12" s="6">
-        <v>0</v>
-      </c>
       <c r="O12" s="6">
         <v>0</v>
       </c>
       <c r="P12" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C13" s="6">
         <v>1008</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="6">
         <v>1009</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
+      <c r="G13" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
         <v>0.03</v>
       </c>
-      <c r="I13" s="6">
+      <c r="J13" s="6">
         <v>110301</v>
       </c>
-      <c r="J13" s="6">
-        <v>1</v>
-      </c>
       <c r="K13" s="6">
         <v>1</v>
       </c>
@@ -3088,43 +3370,46 @@
         <v>1</v>
       </c>
       <c r="M13" s="6">
+        <v>1</v>
+      </c>
+      <c r="N13" s="6">
         <v>10</v>
       </c>
-      <c r="N13" s="6">
-        <v>0</v>
-      </c>
       <c r="O13" s="6">
         <v>0</v>
       </c>
       <c r="P13" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="6">
         <v>1009</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="6">
         <v>1010</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
+      <c r="G14" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
         <v>0.03</v>
       </c>
-      <c r="I14" s="6">
+      <c r="J14" s="6">
         <v>110501</v>
       </c>
-      <c r="J14" s="6">
-        <v>1</v>
-      </c>
       <c r="K14" s="6">
         <v>1</v>
       </c>
@@ -3132,43 +3417,46 @@
         <v>1</v>
       </c>
       <c r="M14" s="6">
+        <v>1</v>
+      </c>
+      <c r="N14" s="6">
         <v>10</v>
       </c>
-      <c r="N14" s="6">
-        <v>0</v>
-      </c>
       <c r="O14" s="6">
         <v>0</v>
       </c>
       <c r="P14" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="6">
         <v>1010</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15" s="6">
         <v>1011</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
+      <c r="G15" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H15" s="6">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6">
         <v>0.03</v>
       </c>
-      <c r="I15" s="6">
+      <c r="J15" s="6">
         <v>118101</v>
       </c>
-      <c r="J15" s="6">
-        <v>1</v>
-      </c>
       <c r="K15" s="6">
         <v>1</v>
       </c>
@@ -3176,43 +3464,46 @@
         <v>1</v>
       </c>
       <c r="M15" s="6">
+        <v>1</v>
+      </c>
+      <c r="N15" s="6">
         <v>10</v>
       </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
       <c r="O15" s="6">
         <v>0</v>
       </c>
       <c r="P15" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="6">
         <v>1011</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="6">
         <v>1012</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
+      <c r="G16" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H16" s="6">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
         <v>0.03</v>
       </c>
-      <c r="I16" s="6">
+      <c r="J16" s="6">
         <v>118201</v>
       </c>
-      <c r="J16" s="6">
-        <v>1</v>
-      </c>
       <c r="K16" s="6">
         <v>1</v>
       </c>
@@ -3220,45 +3511,48 @@
         <v>1</v>
       </c>
       <c r="M16" s="6">
+        <v>1</v>
+      </c>
+      <c r="N16" s="6">
         <v>10</v>
       </c>
-      <c r="N16" s="6">
-        <v>0</v>
-      </c>
       <c r="O16" s="6">
         <v>0</v>
       </c>
       <c r="P16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="6">
         <v>1012</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="6">
         <v>1013</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
+      <c r="G17" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H17" s="6">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="I17" s="6">
+      <c r="J17" s="6">
         <v>120101</v>
       </c>
-      <c r="J17" s="6">
-        <v>0</v>
-      </c>
       <c r="K17" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="6">
         <v>1</v>
@@ -3267,40 +3561,43 @@
         <v>1</v>
       </c>
       <c r="N17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="6">
         <v>0</v>
       </c>
       <c r="P17" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="6">
         <v>1013</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="6">
         <v>1014</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0</v>
+      <c r="G18" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H18" s="6">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
         <v>0.03</v>
       </c>
-      <c r="I18" s="6">
+      <c r="J18" s="6">
         <v>119101</v>
       </c>
-      <c r="J18" s="6">
-        <v>1</v>
-      </c>
       <c r="K18" s="6">
         <v>1</v>
       </c>
@@ -3308,43 +3605,46 @@
         <v>1</v>
       </c>
       <c r="M18" s="6">
+        <v>1</v>
+      </c>
+      <c r="N18" s="6">
         <v>10</v>
       </c>
-      <c r="N18" s="6">
-        <v>0</v>
-      </c>
       <c r="O18" s="6">
         <v>0</v>
       </c>
       <c r="P18" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="6">
         <v>1014</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" s="6">
         <v>1015</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="6">
-        <v>0</v>
+      <c r="G19" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H19" s="6">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6">
         <v>0.03</v>
       </c>
-      <c r="I19" s="6">
+      <c r="J19" s="6">
         <v>119301</v>
       </c>
-      <c r="J19" s="6">
-        <v>1</v>
-      </c>
       <c r="K19" s="6">
         <v>1</v>
       </c>
@@ -3352,43 +3652,46 @@
         <v>1</v>
       </c>
       <c r="M19" s="6">
+        <v>1</v>
+      </c>
+      <c r="N19" s="6">
         <v>10</v>
       </c>
-      <c r="N19" s="6">
-        <v>0</v>
-      </c>
       <c r="O19" s="6">
         <v>0</v>
       </c>
       <c r="P19" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="6">
         <v>1015</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="6">
         <v>1016</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0</v>
+      <c r="G20" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H20" s="6">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6">
         <v>0.03</v>
       </c>
-      <c r="I20" s="6">
+      <c r="J20" s="6">
         <v>119401</v>
       </c>
-      <c r="J20" s="6">
-        <v>1</v>
-      </c>
       <c r="K20" s="6">
         <v>1</v>
       </c>
@@ -3396,43 +3699,46 @@
         <v>1</v>
       </c>
       <c r="M20" s="6">
+        <v>1</v>
+      </c>
+      <c r="N20" s="6">
         <v>10</v>
       </c>
-      <c r="N20" s="6">
-        <v>0</v>
-      </c>
       <c r="O20" s="6">
         <v>0</v>
       </c>
       <c r="P20" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="6">
         <v>1016</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" s="6">
         <v>1017</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="6">
-        <v>0</v>
+      <c r="G21" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H21" s="6">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6">
         <v>0.03</v>
       </c>
-      <c r="I21" s="6">
+      <c r="J21" s="6">
         <v>119201</v>
       </c>
-      <c r="J21" s="6">
-        <v>1</v>
-      </c>
       <c r="K21" s="6">
         <v>1</v>
       </c>
@@ -3440,835 +3746,892 @@
         <v>1</v>
       </c>
       <c r="M21" s="6">
+        <v>1</v>
+      </c>
+      <c r="N21" s="6">
         <v>10</v>
       </c>
-      <c r="N21" s="6">
-        <v>0</v>
-      </c>
       <c r="O21" s="6">
         <v>0</v>
       </c>
       <c r="P21" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="6">
         <v>1017</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="6">
         <v>1018</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0</v>
+      <c r="G22" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H22" s="6">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6">
         <v>0.02</v>
       </c>
-      <c r="I22" s="6">
+      <c r="J22" s="6">
         <v>200101</v>
       </c>
-      <c r="J22" s="6">
-        <v>0</v>
-      </c>
       <c r="K22" s="6">
         <v>0</v>
       </c>
       <c r="L22" s="6">
+        <v>0</v>
+      </c>
+      <c r="M22" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M22" s="6">
+      <c r="N22" s="6">
         <v>0.02</v>
       </c>
-      <c r="N22" s="6">
-        <v>0</v>
-      </c>
       <c r="O22" s="6">
         <v>0</v>
       </c>
       <c r="P22" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="6">
         <v>1018</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="6">
         <v>1019</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="6">
-        <v>0</v>
+      <c r="G23" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H23" s="6">
+        <v>0</v>
+      </c>
+      <c r="I23" s="6">
         <v>0.02</v>
       </c>
-      <c r="I23" s="6">
+      <c r="J23" s="6">
         <v>200201</v>
       </c>
-      <c r="J23" s="6">
-        <v>0</v>
-      </c>
       <c r="K23" s="6">
         <v>0</v>
       </c>
       <c r="L23" s="6">
+        <v>0</v>
+      </c>
+      <c r="M23" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M23" s="6">
+      <c r="N23" s="6">
         <v>0.02</v>
       </c>
-      <c r="N23" s="6">
-        <v>0</v>
-      </c>
       <c r="O23" s="6">
         <v>0</v>
       </c>
       <c r="P23" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="6">
         <v>1019</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="6">
         <v>1020</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="6">
-        <v>0</v>
+      <c r="G24" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H24" s="6">
+        <v>0</v>
+      </c>
+      <c r="I24" s="6">
         <v>0.02</v>
       </c>
-      <c r="I24" s="6">
+      <c r="J24" s="6">
         <v>200301</v>
       </c>
-      <c r="J24" s="6">
-        <v>0</v>
-      </c>
       <c r="K24" s="6">
         <v>0</v>
       </c>
       <c r="L24" s="6">
+        <v>0</v>
+      </c>
+      <c r="M24" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M24" s="6">
+      <c r="N24" s="6">
         <v>0.02</v>
       </c>
-      <c r="N24" s="6">
-        <v>0</v>
-      </c>
       <c r="O24" s="6">
         <v>0</v>
       </c>
       <c r="P24" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C25" s="6">
         <v>1020</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" s="6">
         <v>1021</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="6">
-        <v>0</v>
+      <c r="G25" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="6">
         <v>0.02</v>
       </c>
-      <c r="I25" s="6">
+      <c r="J25" s="6">
         <v>200401</v>
       </c>
-      <c r="J25" s="6">
-        <v>0</v>
-      </c>
       <c r="K25" s="6">
         <v>0</v>
       </c>
       <c r="L25" s="6">
+        <v>0</v>
+      </c>
+      <c r="M25" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M25" s="6">
+      <c r="N25" s="6">
         <v>0.02</v>
       </c>
-      <c r="N25" s="6">
-        <v>0</v>
-      </c>
       <c r="O25" s="6">
         <v>0</v>
       </c>
       <c r="P25" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C26" s="6">
         <v>1021</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" s="6">
         <v>1022</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="6">
-        <v>0</v>
+      <c r="G26" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H26" s="6">
+        <v>0</v>
+      </c>
+      <c r="I26" s="6">
         <v>0.02</v>
       </c>
-      <c r="I26" s="6">
+      <c r="J26" s="6">
         <v>200501</v>
       </c>
-      <c r="J26" s="6">
-        <v>0</v>
-      </c>
       <c r="K26" s="6">
         <v>0</v>
       </c>
       <c r="L26" s="6">
+        <v>0</v>
+      </c>
+      <c r="M26" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M26" s="6">
+      <c r="N26" s="6">
         <v>0.02</v>
       </c>
-      <c r="N26" s="6">
-        <v>0</v>
-      </c>
       <c r="O26" s="6">
         <v>0</v>
       </c>
       <c r="P26" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="6">
         <v>1022</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="6">
         <v>1023</v>
       </c>
-      <c r="F27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0</v>
+      <c r="G27" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H27" s="6">
+        <v>0</v>
+      </c>
+      <c r="I27" s="6">
         <v>0.02</v>
       </c>
-      <c r="I27" s="6">
+      <c r="J27" s="6">
         <v>200601</v>
       </c>
-      <c r="J27" s="6">
-        <v>0</v>
-      </c>
       <c r="K27" s="6">
         <v>0</v>
       </c>
       <c r="L27" s="6">
+        <v>0</v>
+      </c>
+      <c r="M27" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M27" s="6">
+      <c r="N27" s="6">
         <v>0.02</v>
       </c>
-      <c r="N27" s="6">
-        <v>0</v>
-      </c>
       <c r="O27" s="6">
         <v>0</v>
       </c>
       <c r="P27" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C28" s="6">
         <v>1023</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="6">
         <v>1024</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0</v>
+      <c r="G28" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H28" s="6">
+        <v>0</v>
+      </c>
+      <c r="I28" s="6">
         <v>0.02</v>
       </c>
-      <c r="I28" s="6">
+      <c r="J28" s="6">
         <v>200701</v>
       </c>
-      <c r="J28" s="6">
-        <v>0</v>
-      </c>
       <c r="K28" s="6">
         <v>0</v>
       </c>
       <c r="L28" s="6">
+        <v>0</v>
+      </c>
+      <c r="M28" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M28" s="6">
+      <c r="N28" s="6">
         <v>0.02</v>
       </c>
-      <c r="N28" s="6">
-        <v>0</v>
-      </c>
       <c r="O28" s="6">
         <v>0</v>
       </c>
       <c r="P28" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C29" s="6">
         <v>1024</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="6">
         <v>1025</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G29" s="6">
-        <v>0</v>
+      <c r="G29" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H29" s="6">
+        <v>0</v>
+      </c>
+      <c r="I29" s="6">
         <v>0.02</v>
       </c>
-      <c r="I29" s="6">
+      <c r="J29" s="6">
         <v>200801</v>
       </c>
-      <c r="J29" s="6">
-        <v>0</v>
-      </c>
       <c r="K29" s="6">
         <v>0</v>
       </c>
       <c r="L29" s="6">
+        <v>0</v>
+      </c>
+      <c r="M29" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M29" s="6">
+      <c r="N29" s="6">
         <v>0.02</v>
       </c>
-      <c r="N29" s="6">
-        <v>0</v>
-      </c>
       <c r="O29" s="6">
         <v>0</v>
       </c>
       <c r="P29" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C30" s="6">
         <v>1025</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="6">
         <v>1026</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="6">
-        <v>0</v>
+      <c r="G30" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H30" s="6">
+        <v>0</v>
+      </c>
+      <c r="I30" s="6">
         <v>0.02</v>
       </c>
-      <c r="I30" s="6">
+      <c r="J30" s="6">
         <v>200901</v>
       </c>
-      <c r="J30" s="6">
-        <v>0</v>
-      </c>
       <c r="K30" s="6">
         <v>0</v>
       </c>
       <c r="L30" s="6">
+        <v>0</v>
+      </c>
+      <c r="M30" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M30" s="6">
+      <c r="N30" s="6">
         <v>0.02</v>
       </c>
-      <c r="N30" s="6">
-        <v>0</v>
-      </c>
       <c r="O30" s="6">
         <v>0</v>
       </c>
       <c r="P30" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C31" s="6">
         <v>1026</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" s="6">
         <v>1027</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0</v>
+      <c r="G31" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H31" s="6">
+        <v>0</v>
+      </c>
+      <c r="I31" s="6">
         <v>0.02</v>
       </c>
-      <c r="I31" s="6">
+      <c r="J31" s="6">
         <v>201001</v>
       </c>
-      <c r="J31" s="6">
-        <v>0</v>
-      </c>
       <c r="K31" s="6">
         <v>0</v>
       </c>
       <c r="L31" s="6">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M31" s="6">
+      <c r="N31" s="6">
         <v>0.02</v>
       </c>
-      <c r="N31" s="6">
-        <v>0</v>
-      </c>
       <c r="O31" s="6">
         <v>0</v>
       </c>
       <c r="P31" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C32" s="6">
         <v>1027</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="6">
         <v>1028</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="6">
-        <v>0</v>
+      <c r="G32" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H32" s="6">
+        <v>0</v>
+      </c>
+      <c r="I32" s="6">
         <v>0.02</v>
       </c>
-      <c r="I32" s="6">
+      <c r="J32" s="6">
         <v>202201</v>
       </c>
-      <c r="J32" s="6">
-        <v>0</v>
-      </c>
       <c r="K32" s="6">
         <v>0</v>
       </c>
       <c r="L32" s="6">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M32" s="6">
+      <c r="N32" s="6">
         <v>0.02</v>
       </c>
-      <c r="N32" s="6">
-        <v>0</v>
-      </c>
       <c r="O32" s="6">
         <v>0</v>
       </c>
       <c r="P32" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C33" s="6">
         <v>1028</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F33" s="6">
         <v>1030</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G33" s="6">
-        <v>0</v>
+      <c r="G33" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H33" s="6">
+        <v>0</v>
+      </c>
+      <c r="I33" s="6">
         <v>0.02</v>
       </c>
-      <c r="I33" s="6">
+      <c r="J33" s="6">
         <v>202301</v>
       </c>
-      <c r="J33" s="6">
-        <v>0</v>
-      </c>
       <c r="K33" s="6">
         <v>0</v>
       </c>
       <c r="L33" s="6">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M33" s="6">
+      <c r="N33" s="6">
         <v>0.02</v>
       </c>
-      <c r="N33" s="6">
-        <v>0</v>
-      </c>
       <c r="O33" s="6">
         <v>0</v>
       </c>
       <c r="P33" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C34" s="6">
         <v>1030</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34" s="6">
         <v>1031</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G34" s="6">
-        <v>0</v>
+      <c r="G34" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H34" s="6">
+        <v>0</v>
+      </c>
+      <c r="I34" s="6">
         <v>0.03</v>
       </c>
-      <c r="I34" s="6">
+      <c r="J34" s="6">
         <v>203001</v>
       </c>
-      <c r="J34" s="6">
-        <v>0</v>
-      </c>
       <c r="K34" s="6">
         <v>0</v>
       </c>
       <c r="L34" s="6">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M34" s="6">
+      <c r="N34" s="6">
         <v>0.02</v>
       </c>
-      <c r="N34" s="6">
-        <v>0</v>
-      </c>
       <c r="O34" s="6">
         <v>0</v>
       </c>
       <c r="P34" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C35" s="6">
         <v>1031</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" s="6">
         <v>1032</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35" s="6">
-        <v>0</v>
+      <c r="G35" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H35" s="6">
+        <v>0</v>
+      </c>
+      <c r="I35" s="6">
         <v>0.03</v>
       </c>
-      <c r="I35" s="6">
+      <c r="J35" s="6">
         <v>203101</v>
       </c>
-      <c r="J35" s="6">
-        <v>0</v>
-      </c>
       <c r="K35" s="6">
         <v>0</v>
       </c>
       <c r="L35" s="6">
+        <v>0</v>
+      </c>
+      <c r="M35" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M35" s="6">
+      <c r="N35" s="6">
         <v>0.02</v>
       </c>
-      <c r="N35" s="6">
-        <v>0</v>
-      </c>
       <c r="O35" s="6">
         <v>0</v>
       </c>
       <c r="P35" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C36" s="6">
         <v>1032</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" s="6">
         <v>1033</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G36" s="6">
-        <v>0</v>
+      <c r="G36" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H36" s="6">
+        <v>0</v>
+      </c>
+      <c r="I36" s="6">
         <v>0.03</v>
       </c>
-      <c r="I36" s="6">
+      <c r="J36" s="6">
         <v>203201</v>
       </c>
-      <c r="J36" s="6">
-        <v>0</v>
-      </c>
       <c r="K36" s="6">
         <v>0</v>
       </c>
       <c r="L36" s="6">
+        <v>0</v>
+      </c>
+      <c r="M36" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M36" s="6">
+      <c r="N36" s="6">
         <v>0.02</v>
       </c>
-      <c r="N36" s="6">
-        <v>0</v>
-      </c>
       <c r="O36" s="6">
         <v>0</v>
       </c>
       <c r="P36" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C37" s="6">
         <v>1033</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E37" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" s="6">
         <v>1034</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G37" s="6">
-        <v>0</v>
+      <c r="G37" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H37" s="6">
+        <v>0</v>
+      </c>
+      <c r="I37" s="6">
         <v>0.03</v>
       </c>
-      <c r="I37" s="6">
+      <c r="J37" s="6">
         <v>203301</v>
       </c>
-      <c r="J37" s="6">
-        <v>0</v>
-      </c>
       <c r="K37" s="6">
         <v>0</v>
       </c>
       <c r="L37" s="6">
+        <v>0</v>
+      </c>
+      <c r="M37" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M37" s="6">
+      <c r="N37" s="6">
         <v>0.02</v>
       </c>
-      <c r="N37" s="6">
-        <v>0</v>
-      </c>
       <c r="O37" s="6">
         <v>0</v>
       </c>
       <c r="P37" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C38" s="6">
         <v>1034</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F38" s="6">
         <v>1035</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G38" s="6">
-        <v>0</v>
+      <c r="G38" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H38" s="6">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6">
         <v>0.02</v>
       </c>
-      <c r="I38" s="6">
+      <c r="J38" s="6">
         <v>203601</v>
       </c>
-      <c r="J38" s="6">
-        <v>0</v>
-      </c>
       <c r="K38" s="6">
         <v>0</v>
       </c>
       <c r="L38" s="6">
+        <v>0</v>
+      </c>
+      <c r="M38" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M38" s="6">
+      <c r="N38" s="6">
         <v>0.02</v>
       </c>
-      <c r="N38" s="6">
-        <v>0</v>
-      </c>
       <c r="O38" s="6">
         <v>0</v>
       </c>
       <c r="P38" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C39" s="6">
         <v>1035</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="6">
         <v>1036</v>
       </c>
-      <c r="F39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G39" s="6">
-        <v>0</v>
+      <c r="G39" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H39" s="6">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6">
         <v>0.02</v>
       </c>
-      <c r="I39" s="6">
+      <c r="J39" s="6">
         <v>220101</v>
       </c>
-      <c r="J39" s="6">
-        <v>0</v>
-      </c>
       <c r="K39" s="6">
         <v>0</v>
       </c>
       <c r="L39" s="6">
+        <v>0</v>
+      </c>
+      <c r="M39" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M39" s="6">
+      <c r="N39" s="6">
         <v>0.02</v>
       </c>
-      <c r="N39" s="6">
-        <v>0</v>
-      </c>
       <c r="O39" s="6">
         <v>0</v>
       </c>
       <c r="P39" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C40" s="6">
         <v>1036</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F40" s="6">
         <v>1037</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G40" s="6">
-        <v>0</v>
+      <c r="G40" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H40" s="6">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6">
         <v>0.02</v>
       </c>
-      <c r="I40" s="6">
+      <c r="J40" s="6">
         <v>105101</v>
       </c>
-      <c r="J40" s="6">
-        <v>1</v>
-      </c>
       <c r="K40" s="6">
         <v>1</v>
       </c>
@@ -4276,43 +4639,46 @@
         <v>1</v>
       </c>
       <c r="M40" s="6">
+        <v>1</v>
+      </c>
+      <c r="N40" s="6">
         <v>4</v>
       </c>
-      <c r="N40" s="6">
-        <v>0</v>
-      </c>
       <c r="O40" s="6">
         <v>0</v>
       </c>
       <c r="P40" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C41" s="6">
         <v>1037</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="6">
         <v>1038</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G41" s="6">
-        <v>0</v>
+      <c r="G41" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H41" s="6">
+        <v>0</v>
+      </c>
+      <c r="I41" s="6">
         <v>0.02</v>
       </c>
-      <c r="I41" s="6">
+      <c r="J41" s="6">
         <v>105301</v>
       </c>
-      <c r="J41" s="6">
-        <v>1</v>
-      </c>
       <c r="K41" s="6">
         <v>1</v>
       </c>
@@ -4320,43 +4686,46 @@
         <v>1</v>
       </c>
       <c r="M41" s="6">
+        <v>1</v>
+      </c>
+      <c r="N41" s="6">
         <v>4</v>
       </c>
-      <c r="N41" s="6">
-        <v>0</v>
-      </c>
       <c r="O41" s="6">
         <v>0</v>
       </c>
       <c r="P41" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C42" s="6">
         <v>1038</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F42" s="6">
         <v>1039</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="6">
-        <v>0</v>
+      <c r="G42" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H42" s="6">
+        <v>0</v>
+      </c>
+      <c r="I42" s="6">
         <v>0.02</v>
       </c>
-      <c r="I42" s="6">
+      <c r="J42" s="6">
         <v>105501</v>
       </c>
-      <c r="J42" s="6">
-        <v>1</v>
-      </c>
       <c r="K42" s="6">
         <v>1</v>
       </c>
@@ -4364,43 +4733,46 @@
         <v>1</v>
       </c>
       <c r="M42" s="6">
+        <v>1</v>
+      </c>
+      <c r="N42" s="6">
         <v>4</v>
       </c>
-      <c r="N42" s="6">
-        <v>0</v>
-      </c>
       <c r="O42" s="6">
         <v>0</v>
       </c>
       <c r="P42" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C43" s="6">
         <v>1039</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F43" s="6">
         <v>1040</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G43" s="6">
-        <v>0</v>
+      <c r="G43" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H43" s="6">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6">
         <v>0.02</v>
       </c>
-      <c r="I43" s="6">
+      <c r="J43" s="6">
         <v>105401</v>
       </c>
-      <c r="J43" s="6">
-        <v>1</v>
-      </c>
       <c r="K43" s="6">
         <v>1</v>
       </c>
@@ -4408,43 +4780,46 @@
         <v>1</v>
       </c>
       <c r="M43" s="6">
+        <v>1</v>
+      </c>
+      <c r="N43" s="6">
         <v>4</v>
       </c>
-      <c r="N43" s="6">
-        <v>0</v>
-      </c>
       <c r="O43" s="6">
         <v>0</v>
       </c>
       <c r="P43" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C44" s="6">
         <v>1040</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F44" s="6">
         <v>1041</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G44" s="6">
-        <v>0</v>
+      <c r="G44" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H44" s="6">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6">
         <v>0.02</v>
       </c>
-      <c r="I44" s="6">
+      <c r="J44" s="6">
         <v>105201</v>
       </c>
-      <c r="J44" s="6">
-        <v>1</v>
-      </c>
       <c r="K44" s="6">
         <v>1</v>
       </c>
@@ -4452,351 +4827,375 @@
         <v>1</v>
       </c>
       <c r="M44" s="6">
+        <v>1</v>
+      </c>
+      <c r="N44" s="6">
         <v>4</v>
       </c>
-      <c r="N44" s="6">
-        <v>0</v>
-      </c>
       <c r="O44" s="6">
         <v>0</v>
       </c>
       <c r="P44" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C45" s="6">
         <v>1041</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="6">
         <v>1042</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G45" s="6">
-        <v>0</v>
+      <c r="G45" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H45" s="6">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6">
         <v>0.02</v>
       </c>
-      <c r="I45" s="6">
+      <c r="J45" s="6">
         <v>205101</v>
       </c>
-      <c r="J45" s="6">
-        <v>0</v>
-      </c>
       <c r="K45" s="6">
         <v>0</v>
       </c>
       <c r="L45" s="6">
+        <v>0</v>
+      </c>
+      <c r="M45" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M45" s="6">
+      <c r="N45" s="6">
         <v>0.02</v>
       </c>
-      <c r="N45" s="6">
-        <v>0</v>
-      </c>
       <c r="O45" s="6">
         <v>0</v>
       </c>
       <c r="P45" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C46" s="6">
         <v>1042</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E46" s="6">
+      <c r="E46" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F46" s="6">
         <v>1043</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46" s="6">
-        <v>0</v>
+      <c r="G46" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H46" s="6">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6">
         <v>0.02</v>
       </c>
-      <c r="I46" s="6">
+      <c r="J46" s="6">
         <v>205201</v>
       </c>
-      <c r="J46" s="6">
-        <v>0</v>
-      </c>
       <c r="K46" s="6">
         <v>0</v>
       </c>
       <c r="L46" s="6">
+        <v>0</v>
+      </c>
+      <c r="M46" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M46" s="6">
+      <c r="N46" s="6">
         <v>0.02</v>
       </c>
-      <c r="N46" s="6">
-        <v>0</v>
-      </c>
       <c r="O46" s="6">
         <v>0</v>
       </c>
       <c r="P46" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C47" s="6">
         <v>1043</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E47" s="6">
+      <c r="E47" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F47" s="6">
         <v>1044</v>
       </c>
-      <c r="F47" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G47" s="6">
-        <v>0</v>
+      <c r="G47" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H47" s="6">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6">
         <v>0.02</v>
       </c>
-      <c r="I47" s="6">
+      <c r="J47" s="6">
         <v>205301</v>
       </c>
-      <c r="J47" s="6">
-        <v>0</v>
-      </c>
       <c r="K47" s="6">
         <v>0</v>
       </c>
       <c r="L47" s="6">
+        <v>0</v>
+      </c>
+      <c r="M47" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M47" s="6">
+      <c r="N47" s="6">
         <v>0.02</v>
       </c>
-      <c r="N47" s="6">
-        <v>0</v>
-      </c>
       <c r="O47" s="6">
         <v>0</v>
       </c>
       <c r="P47" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C48" s="6">
         <v>1044</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E48" s="6">
+      <c r="E48" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F48" s="6">
         <v>1045</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G48" s="6">
-        <v>0</v>
+      <c r="G48" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H48" s="6">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6">
         <v>0.02</v>
       </c>
-      <c r="I48" s="6">
+      <c r="J48" s="6">
         <v>205401</v>
       </c>
-      <c r="J48" s="6">
-        <v>0</v>
-      </c>
       <c r="K48" s="6">
         <v>0</v>
       </c>
       <c r="L48" s="6">
+        <v>0</v>
+      </c>
+      <c r="M48" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M48" s="6">
+      <c r="N48" s="6">
         <v>0.02</v>
       </c>
-      <c r="N48" s="6">
-        <v>0</v>
-      </c>
       <c r="O48" s="6">
         <v>0</v>
       </c>
       <c r="P48" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C49" s="6">
         <v>1045</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E49" s="6">
+      <c r="E49" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="F49" s="6">
         <v>1046</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" s="6">
-        <v>0</v>
+      <c r="G49" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H49" s="6">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6">
         <v>0.02</v>
       </c>
-      <c r="I49" s="6">
+      <c r="J49" s="6">
         <v>204301</v>
       </c>
-      <c r="J49" s="6">
-        <v>0</v>
-      </c>
       <c r="K49" s="6">
         <v>0</v>
       </c>
       <c r="L49" s="6">
+        <v>0</v>
+      </c>
+      <c r="M49" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M49" s="6">
+      <c r="N49" s="6">
         <v>0.02</v>
       </c>
-      <c r="N49" s="6">
-        <v>0</v>
-      </c>
       <c r="O49" s="6">
         <v>0</v>
       </c>
       <c r="P49" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C50" s="6">
         <v>1046</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E50" s="6">
+      <c r="E50" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F50" s="6">
         <v>1047</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" s="6">
-        <v>0</v>
+      <c r="G50" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H50" s="6">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6">
         <v>0.02</v>
       </c>
-      <c r="I50" s="6">
+      <c r="J50" s="6">
         <v>213101</v>
       </c>
-      <c r="J50" s="6">
-        <v>0</v>
-      </c>
       <c r="K50" s="6">
         <v>0</v>
       </c>
       <c r="L50" s="6">
+        <v>0</v>
+      </c>
+      <c r="M50" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M50" s="6">
+      <c r="N50" s="6">
         <v>0.02</v>
       </c>
-      <c r="N50" s="6">
-        <v>0</v>
-      </c>
       <c r="O50" s="6">
         <v>0</v>
       </c>
       <c r="P50" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C51" s="6">
         <v>1047</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E51" s="6">
-        <v>0</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G51" s="6">
-        <v>0</v>
+      <c r="E51" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6">
         <v>0.02</v>
       </c>
-      <c r="I51" s="6">
+      <c r="J51" s="6">
         <v>207101</v>
       </c>
-      <c r="J51" s="6">
-        <v>0</v>
-      </c>
       <c r="K51" s="6">
         <v>0</v>
       </c>
       <c r="L51" s="6">
+        <v>0</v>
+      </c>
+      <c r="M51" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M51" s="6">
+      <c r="N51" s="6">
         <v>0.02</v>
       </c>
-      <c r="N51" s="6">
-        <v>0</v>
-      </c>
       <c r="O51" s="6">
         <v>0</v>
       </c>
       <c r="P51" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C52" s="6">
         <v>2001</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F52" s="6">
         <v>2002</v>
       </c>
-      <c r="F52" s="6">
-        <v>1</v>
-      </c>
       <c r="G52" s="6">
         <v>1</v>
       </c>
       <c r="H52" s="6">
+        <v>1</v>
+      </c>
+      <c r="I52" s="6">
         <v>0.01</v>
       </c>
-      <c r="I52" s="6">
+      <c r="J52" s="6">
         <v>68000001</v>
       </c>
-      <c r="J52" s="6">
-        <v>0</v>
-      </c>
       <c r="K52" s="6">
         <v>0</v>
       </c>
@@ -4813,34 +5212,37 @@
         <v>0</v>
       </c>
       <c r="P52" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C53" s="6">
         <v>2002</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F53" s="6">
         <v>2003</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" s="6">
+      <c r="G53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H53" s="6">
         <v>6</v>
       </c>
-      <c r="H53" s="6">
+      <c r="I53" s="6">
         <v>0.03</v>
       </c>
-      <c r="I53" s="6">
+      <c r="J53" s="6">
         <v>68000002</v>
       </c>
-      <c r="J53" s="6">
-        <v>0</v>
-      </c>
       <c r="K53" s="6">
         <v>0</v>
       </c>
@@ -4851,40 +5253,43 @@
         <v>0</v>
       </c>
       <c r="N53" s="6">
+        <v>0</v>
+      </c>
+      <c r="O53" s="6">
         <v>100</v>
       </c>
-      <c r="O53" s="6">
-        <v>0</v>
-      </c>
       <c r="P53" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C54" s="6">
         <v>2003</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F54" s="6">
         <v>2004</v>
       </c>
-      <c r="F54" s="6">
+      <c r="G54" s="6">
         <v>2</v>
       </c>
-      <c r="G54" s="6">
+      <c r="H54" s="6">
         <v>6</v>
       </c>
-      <c r="H54" s="6">
+      <c r="I54" s="6">
         <v>0.01</v>
       </c>
-      <c r="I54" s="6">
+      <c r="J54" s="6">
         <v>68000003</v>
       </c>
-      <c r="J54" s="6">
-        <v>0</v>
-      </c>
       <c r="K54" s="6">
         <v>0</v>
       </c>
@@ -4895,40 +5300,43 @@
         <v>0</v>
       </c>
       <c r="N54" s="6">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6">
         <v>100</v>
       </c>
-      <c r="O54" s="6">
-        <v>0</v>
-      </c>
       <c r="P54" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C55" s="6">
         <v>2004</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E55" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F55" s="6">
         <v>2005</v>
       </c>
-      <c r="F55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G55" s="6">
-        <v>1</v>
+      <c r="G55" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H55" s="6">
+        <v>1</v>
+      </c>
+      <c r="I55" s="6">
         <v>0.03</v>
       </c>
-      <c r="I55" s="6">
+      <c r="J55" s="6">
         <v>68000004</v>
       </c>
-      <c r="J55" s="6">
-        <v>0</v>
-      </c>
       <c r="K55" s="6">
         <v>0</v>
       </c>
@@ -4939,40 +5347,43 @@
         <v>0</v>
       </c>
       <c r="N55" s="6">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6">
         <v>100</v>
       </c>
-      <c r="O55" s="6">
-        <v>0</v>
-      </c>
       <c r="P55" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C56" s="6">
         <v>2005</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E56" s="6">
+      <c r="E56" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F56" s="6">
         <v>2006</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G56" s="6">
-        <v>0</v>
+      <c r="G56" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H56" s="6">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6">
         <v>0.03</v>
       </c>
-      <c r="I56" s="6">
+      <c r="J56" s="6">
         <v>68000005</v>
       </c>
-      <c r="J56" s="6">
-        <v>0</v>
-      </c>
       <c r="K56" s="6">
         <v>0</v>
       </c>
@@ -4983,40 +5394,43 @@
         <v>0</v>
       </c>
       <c r="N56" s="6">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6">
         <v>100</v>
       </c>
-      <c r="O56" s="6">
-        <v>0</v>
-      </c>
       <c r="P56" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C57" s="6">
         <v>2006</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="6">
+      <c r="E57" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F57" s="6">
         <v>2007</v>
       </c>
-      <c r="F57" s="6">
+      <c r="G57" s="6">
         <v>3</v>
       </c>
-      <c r="G57" s="6">
-        <v>0</v>
-      </c>
       <c r="H57" s="6">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6">
         <v>0.01</v>
       </c>
-      <c r="I57" s="6">
+      <c r="J57" s="6">
         <v>68000006</v>
       </c>
-      <c r="J57" s="6">
-        <v>0</v>
-      </c>
       <c r="K57" s="6">
         <v>0</v>
       </c>
@@ -5027,40 +5441,43 @@
         <v>0</v>
       </c>
       <c r="N57" s="6">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6">
         <v>100</v>
       </c>
-      <c r="O57" s="6">
-        <v>0</v>
-      </c>
       <c r="P57" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C58" s="6">
         <v>2007</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E58" s="6">
+      <c r="E58" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F58" s="6">
         <v>2008</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G58" s="6">
+      <c r="G58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" s="6">
         <v>2</v>
       </c>
-      <c r="H58" s="6">
+      <c r="I58" s="6">
         <v>0.01</v>
       </c>
-      <c r="I58" s="6">
+      <c r="J58" s="6">
         <v>68000007</v>
       </c>
-      <c r="J58" s="6">
-        <v>0</v>
-      </c>
       <c r="K58" s="6">
         <v>0</v>
       </c>
@@ -5071,40 +5488,43 @@
         <v>0</v>
       </c>
       <c r="N58" s="6">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6">
         <v>100</v>
       </c>
-      <c r="O58" s="6">
-        <v>0</v>
-      </c>
       <c r="P58" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C59" s="6">
         <v>2008</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E59" s="6">
+      <c r="E59" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F59" s="6">
         <v>2009</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" s="6">
+      <c r="G59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H59" s="6">
         <v>7</v>
       </c>
-      <c r="H59" s="6">
+      <c r="I59" s="6">
         <v>0.03</v>
       </c>
-      <c r="I59" s="6">
+      <c r="J59" s="6">
         <v>68000008</v>
       </c>
-      <c r="J59" s="6">
-        <v>0</v>
-      </c>
       <c r="K59" s="6">
         <v>0</v>
       </c>
@@ -5121,34 +5541,37 @@
         <v>0</v>
       </c>
       <c r="P59" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C60" s="6">
         <v>2009</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E60" s="6">
+      <c r="E60" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="F60" s="6">
         <v>2010</v>
       </c>
-      <c r="F60" s="6">
+      <c r="G60" s="6">
         <v>6</v>
       </c>
-      <c r="G60" s="6">
+      <c r="H60" s="6">
         <v>2</v>
       </c>
-      <c r="H60" s="6">
+      <c r="I60" s="6">
         <v>0.01</v>
       </c>
-      <c r="I60" s="6">
+      <c r="J60" s="6">
         <v>68000009</v>
       </c>
-      <c r="J60" s="6">
-        <v>0</v>
-      </c>
       <c r="K60" s="6">
         <v>0</v>
       </c>
@@ -5159,40 +5582,43 @@
         <v>0</v>
       </c>
       <c r="N60" s="6">
+        <v>0</v>
+      </c>
+      <c r="O60" s="6">
         <v>100</v>
       </c>
-      <c r="O60" s="6">
-        <v>0</v>
-      </c>
       <c r="P60" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C61" s="6">
         <v>2010</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E61" s="6">
+      <c r="E61" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="F61" s="6">
         <v>2011</v>
       </c>
-      <c r="F61" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G61" s="6">
-        <v>0</v>
+      <c r="G61" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H61" s="6">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6">
         <v>0.03</v>
       </c>
-      <c r="I61" s="6">
+      <c r="J61" s="6">
         <v>68000010</v>
       </c>
-      <c r="J61" s="6">
-        <v>0</v>
-      </c>
       <c r="K61" s="6">
         <v>0</v>
       </c>
@@ -5209,34 +5635,37 @@
         <v>0</v>
       </c>
       <c r="P61" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C62" s="6">
         <v>2011</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E62" s="6">
+      <c r="E62" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F62" s="6">
         <v>2012</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="6">
+      <c r="G62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H62" s="6">
         <v>7</v>
       </c>
-      <c r="H62" s="6">
+      <c r="I62" s="6">
         <v>0.01</v>
       </c>
-      <c r="I62" s="6">
+      <c r="J62" s="6">
         <v>68000011</v>
       </c>
-      <c r="J62" s="6">
-        <v>0</v>
-      </c>
       <c r="K62" s="6">
         <v>0</v>
       </c>
@@ -5247,40 +5676,43 @@
         <v>0</v>
       </c>
       <c r="N62" s="6">
+        <v>0</v>
+      </c>
+      <c r="O62" s="6">
         <v>100</v>
       </c>
-      <c r="O62" s="6">
-        <v>0</v>
-      </c>
       <c r="P62" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C63" s="6">
         <v>2012</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E63" s="6">
+      <c r="E63" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F63" s="6">
         <v>2013</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="6">
+      <c r="G63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H63" s="6">
         <v>3</v>
       </c>
-      <c r="H63" s="6">
+      <c r="I63" s="6">
         <v>0.03</v>
       </c>
-      <c r="I63" s="6">
+      <c r="J63" s="6">
         <v>68000012</v>
       </c>
-      <c r="J63" s="6">
-        <v>0</v>
-      </c>
       <c r="K63" s="6">
         <v>0</v>
       </c>
@@ -5291,40 +5723,43 @@
         <v>0</v>
       </c>
       <c r="N63" s="6">
+        <v>0</v>
+      </c>
+      <c r="O63" s="6">
         <v>100</v>
       </c>
-      <c r="O63" s="6">
-        <v>0</v>
-      </c>
       <c r="P63" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C64" s="6">
         <v>2013</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E64" s="6">
+      <c r="E64" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F64" s="6">
         <v>2014</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G64" s="6">
+      <c r="G64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H64" s="6">
         <v>4</v>
       </c>
-      <c r="H64" s="6">
+      <c r="I64" s="6">
         <v>0.03</v>
       </c>
-      <c r="I64" s="6">
+      <c r="J64" s="6">
         <v>68000013</v>
       </c>
-      <c r="J64" s="6">
-        <v>0</v>
-      </c>
       <c r="K64" s="6">
         <v>0</v>
       </c>
@@ -5335,40 +5770,43 @@
         <v>0</v>
       </c>
       <c r="N64" s="6">
+        <v>0</v>
+      </c>
+      <c r="O64" s="6">
         <v>100</v>
       </c>
-      <c r="O64" s="6">
-        <v>0</v>
-      </c>
       <c r="P64" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C65" s="6">
         <v>2014</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E65" s="6">
+      <c r="E65" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F65" s="6">
         <v>2015</v>
       </c>
-      <c r="F65" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G65" s="6">
+      <c r="G65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H65" s="6">
         <v>3</v>
       </c>
-      <c r="H65" s="6">
+      <c r="I65" s="6">
         <v>0.03</v>
       </c>
-      <c r="I65" s="6">
+      <c r="J65" s="6">
         <v>68000014</v>
       </c>
-      <c r="J65" s="6">
-        <v>0</v>
-      </c>
       <c r="K65" s="6">
         <v>0</v>
       </c>
@@ -5385,34 +5823,37 @@
         <v>0</v>
       </c>
       <c r="P65" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C66" s="6">
         <v>2015</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E66" s="6">
+      <c r="E66" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F66" s="6">
         <v>2016</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G66" s="6">
+      <c r="G66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H66" s="6">
         <v>4</v>
       </c>
-      <c r="H66" s="6">
+      <c r="I66" s="6">
         <v>0.03</v>
       </c>
-      <c r="I66" s="6">
+      <c r="J66" s="6">
         <v>68000015</v>
       </c>
-      <c r="J66" s="6">
-        <v>0</v>
-      </c>
       <c r="K66" s="6">
         <v>0</v>
       </c>
@@ -5429,34 +5870,37 @@
         <v>0</v>
       </c>
       <c r="P66" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C67" s="6">
         <v>2016</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E67" s="6">
+      <c r="E67" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F67" s="6">
         <v>2017</v>
       </c>
-      <c r="F67" s="6">
-        <v>1</v>
-      </c>
       <c r="G67" s="6">
+        <v>1</v>
+      </c>
+      <c r="H67" s="6">
         <v>5</v>
       </c>
-      <c r="H67" s="6">
+      <c r="I67" s="6">
         <v>0.03</v>
       </c>
-      <c r="I67" s="6">
+      <c r="J67" s="6">
         <v>68000016</v>
       </c>
-      <c r="J67" s="6">
-        <v>0</v>
-      </c>
       <c r="K67" s="6">
         <v>0</v>
       </c>
@@ -5473,34 +5917,37 @@
         <v>0</v>
       </c>
       <c r="P67" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="3:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C68" s="6">
         <v>2017</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E68" s="6">
+      <c r="E68" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F68" s="6">
         <v>2101</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="6">
+      <c r="G68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H68" s="6">
         <v>5</v>
       </c>
-      <c r="H68" s="6">
+      <c r="I68" s="6">
         <v>0.01</v>
       </c>
-      <c r="I68" s="6">
+      <c r="J68" s="6">
         <v>68000017</v>
       </c>
-      <c r="J68" s="6">
-        <v>0</v>
-      </c>
       <c r="K68" s="6">
         <v>0</v>
       </c>
@@ -5511,40 +5958,43 @@
         <v>0</v>
       </c>
       <c r="N68" s="6">
+        <v>0</v>
+      </c>
+      <c r="O68" s="6">
         <v>100</v>
       </c>
-      <c r="O68" s="6">
-        <v>0</v>
-      </c>
       <c r="P68" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C69" s="6">
         <v>2101</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E69" s="6">
+      <c r="E69" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F69" s="6">
         <v>2102</v>
       </c>
-      <c r="F69" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G69" s="6">
-        <v>0</v>
+      <c r="G69" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H69" s="6">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6">
         <v>0.02</v>
       </c>
-      <c r="I69" s="6">
+      <c r="J69" s="6">
         <v>68000101</v>
       </c>
-      <c r="J69" s="6">
-        <v>0</v>
-      </c>
       <c r="K69" s="6">
         <v>0</v>
       </c>
@@ -5555,40 +6005,43 @@
         <v>0</v>
       </c>
       <c r="N69" s="6">
+        <v>0</v>
+      </c>
+      <c r="O69" s="6">
         <v>100</v>
       </c>
-      <c r="O69" s="6">
-        <v>0</v>
-      </c>
       <c r="P69" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C70" s="6">
         <v>2102</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E70" s="6">
+      <c r="E70" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F70" s="6">
         <v>2103</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G70" s="6">
-        <v>1</v>
+      <c r="G70" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H70" s="6">
+        <v>1</v>
+      </c>
+      <c r="I70" s="6">
         <v>0.05</v>
       </c>
-      <c r="I70" s="6">
+      <c r="J70" s="6">
         <v>68000102</v>
       </c>
-      <c r="J70" s="6">
-        <v>0</v>
-      </c>
       <c r="K70" s="6">
         <v>0</v>
       </c>
@@ -5605,34 +6058,37 @@
         <v>0</v>
       </c>
       <c r="P70" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C71" s="6">
         <v>2103</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="E71" s="6">
+      <c r="E71" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F71" s="6">
         <v>2104</v>
       </c>
-      <c r="F71" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G71" s="6">
+      <c r="G71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H71" s="6">
         <v>2</v>
       </c>
-      <c r="H71" s="6">
+      <c r="I71" s="6">
         <v>0.05</v>
       </c>
-      <c r="I71" s="6">
+      <c r="J71" s="6">
         <v>68000103</v>
       </c>
-      <c r="J71" s="6">
-        <v>0</v>
-      </c>
       <c r="K71" s="6">
         <v>0</v>
       </c>
@@ -5649,34 +6105,37 @@
         <v>0</v>
       </c>
       <c r="P71" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C72" s="6">
         <v>2104</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E72" s="6">
+      <c r="E72" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F72" s="6">
         <v>2105</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G72" s="6">
-        <v>0</v>
+      <c r="G72" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H72" s="6">
+        <v>0</v>
+      </c>
+      <c r="I72" s="6">
         <v>0.01</v>
       </c>
-      <c r="I72" s="6">
+      <c r="J72" s="6">
         <v>68000104</v>
       </c>
-      <c r="J72" s="6">
-        <v>0</v>
-      </c>
       <c r="K72" s="6">
         <v>0</v>
       </c>
@@ -5693,34 +6152,37 @@
         <v>0</v>
       </c>
       <c r="P72" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C73" s="6">
         <v>2105</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E73" s="6">
+      <c r="E73" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F73" s="6">
         <v>2106</v>
       </c>
-      <c r="F73" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G73" s="6">
-        <v>0</v>
+      <c r="G73" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H73" s="6">
+        <v>0</v>
+      </c>
+      <c r="I73" s="6">
         <v>0.02</v>
       </c>
-      <c r="I73" s="6">
+      <c r="J73" s="6">
         <v>68000105</v>
       </c>
-      <c r="J73" s="6">
-        <v>0</v>
-      </c>
       <c r="K73" s="6">
         <v>0</v>
       </c>
@@ -5737,34 +6199,37 @@
         <v>0</v>
       </c>
       <c r="P73" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C74" s="6">
         <v>2106</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E74" s="6">
+      <c r="E74" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F74" s="6">
         <v>2107</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G74" s="6">
-        <v>0</v>
+      <c r="G74" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H74" s="6">
+        <v>0</v>
+      </c>
+      <c r="I74" s="6">
         <v>0.02</v>
       </c>
-      <c r="I74" s="6">
+      <c r="J74" s="6">
         <v>68000106</v>
       </c>
-      <c r="J74" s="6">
-        <v>0</v>
-      </c>
       <c r="K74" s="6">
         <v>0</v>
       </c>
@@ -5781,34 +6246,37 @@
         <v>0</v>
       </c>
       <c r="P74" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C75" s="6">
         <v>2107</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E75" s="6">
+      <c r="E75" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F75" s="6">
         <v>2108</v>
       </c>
-      <c r="F75" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G75" s="6">
-        <v>0</v>
+      <c r="G75" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H75" s="6">
+        <v>0</v>
+      </c>
+      <c r="I75" s="6">
         <v>0.03</v>
       </c>
-      <c r="I75" s="6">
+      <c r="J75" s="6">
         <v>68000107</v>
       </c>
-      <c r="J75" s="6">
-        <v>0</v>
-      </c>
       <c r="K75" s="6">
         <v>0</v>
       </c>
@@ -5825,34 +6293,37 @@
         <v>0</v>
       </c>
       <c r="P75" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C76" s="6">
         <v>2108</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E76" s="6">
+      <c r="E76" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F76" s="6">
         <v>2109</v>
       </c>
-      <c r="F76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G76" s="6">
-        <v>0</v>
+      <c r="G76" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H76" s="6">
+        <v>0</v>
+      </c>
+      <c r="I76" s="6">
         <v>0.02</v>
       </c>
-      <c r="I76" s="6">
+      <c r="J76" s="6">
         <v>68000108</v>
       </c>
-      <c r="J76" s="6">
-        <v>0</v>
-      </c>
       <c r="K76" s="6">
         <v>0</v>
       </c>
@@ -5869,34 +6340,37 @@
         <v>0</v>
       </c>
       <c r="P76" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C77" s="6">
         <v>2109</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E77" s="6">
+      <c r="E77" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F77" s="6">
         <v>2110</v>
       </c>
-      <c r="F77" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G77" s="6">
-        <v>0</v>
+      <c r="G77" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H77" s="6">
+        <v>0</v>
+      </c>
+      <c r="I77" s="6">
         <v>0.04</v>
       </c>
-      <c r="I77" s="6">
+      <c r="J77" s="6">
         <v>68000109</v>
       </c>
-      <c r="J77" s="6">
-        <v>0</v>
-      </c>
       <c r="K77" s="6">
         <v>0</v>
       </c>
@@ -5913,34 +6387,37 @@
         <v>0</v>
       </c>
       <c r="P77" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="6">
         <v>2110</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E78" s="6">
+      <c r="E78" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F78" s="6">
         <v>2111</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G78" s="6">
+      <c r="G78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H78" s="6">
         <v>3</v>
       </c>
-      <c r="H78" s="6">
+      <c r="I78" s="6">
         <v>0.02</v>
       </c>
-      <c r="I78" s="6">
+      <c r="J78" s="6">
         <v>68000110</v>
       </c>
-      <c r="J78" s="6">
-        <v>0</v>
-      </c>
       <c r="K78" s="6">
         <v>0</v>
       </c>
@@ -5951,40 +6428,43 @@
         <v>0</v>
       </c>
       <c r="N78" s="6">
+        <v>0</v>
+      </c>
+      <c r="O78" s="6">
         <v>100</v>
       </c>
-      <c r="O78" s="6">
-        <v>0</v>
-      </c>
       <c r="P78" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C79" s="6">
         <v>2111</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E79" s="6">
+      <c r="E79" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F79" s="6">
         <v>2112</v>
       </c>
-      <c r="F79" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G79" s="6">
+      <c r="G79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H79" s="6">
         <v>4</v>
       </c>
-      <c r="H79" s="6">
+      <c r="I79" s="6">
         <v>0.02</v>
       </c>
-      <c r="I79" s="6">
+      <c r="J79" s="6">
         <v>68000111</v>
       </c>
-      <c r="J79" s="6">
-        <v>0</v>
-      </c>
       <c r="K79" s="6">
         <v>0</v>
       </c>
@@ -5995,40 +6475,43 @@
         <v>0</v>
       </c>
       <c r="N79" s="6">
+        <v>0</v>
+      </c>
+      <c r="O79" s="6">
         <v>100</v>
       </c>
-      <c r="O79" s="6">
-        <v>0</v>
-      </c>
       <c r="P79" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C80" s="6">
         <v>2112</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E80" s="6">
+      <c r="E80" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F80" s="6">
         <v>2113</v>
       </c>
-      <c r="F80" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G80" s="6">
+      <c r="G80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H80" s="6">
         <v>5</v>
       </c>
-      <c r="H80" s="6">
+      <c r="I80" s="6">
         <v>0.02</v>
       </c>
-      <c r="I80" s="6">
+      <c r="J80" s="6">
         <v>68000112</v>
       </c>
-      <c r="J80" s="6">
-        <v>0</v>
-      </c>
       <c r="K80" s="6">
         <v>0</v>
       </c>
@@ -6039,40 +6522,43 @@
         <v>0</v>
       </c>
       <c r="N80" s="6">
+        <v>0</v>
+      </c>
+      <c r="O80" s="6">
         <v>100</v>
       </c>
-      <c r="O80" s="6">
-        <v>0</v>
-      </c>
       <c r="P80" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C81" s="6">
         <v>2113</v>
       </c>
       <c r="D81" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E81" s="6">
-        <v>0</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G81" s="6">
+      <c r="E81" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F81" s="6">
+        <v>0</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H81" s="6">
         <v>6</v>
       </c>
-      <c r="H81" s="6">
+      <c r="I81" s="6">
         <v>0.02</v>
       </c>
-      <c r="I81" s="6">
+      <c r="J81" s="6">
         <v>68000113</v>
       </c>
-      <c r="J81" s="6">
-        <v>0</v>
-      </c>
       <c r="K81" s="6">
         <v>0</v>
       </c>
@@ -6083,16 +6569,19 @@
         <v>0</v>
       </c>
       <c r="N81" s="6">
+        <v>0</v>
+      </c>
+      <c r="O81" s="6">
         <v>100</v>
       </c>
-      <c r="O81" s="6">
-        <v>0</v>
-      </c>
       <c r="P81" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="7"/>
       <c r="C82" s="6">
         <v>3101</v>
@@ -6100,44 +6589,47 @@
       <c r="D82" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E82" s="6">
-        <v>0</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G82" s="6">
-        <v>0</v>
+      <c r="E82" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" s="6">
+        <v>0</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H82" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" s="6">
+        <v>1</v>
+      </c>
+      <c r="J82" s="6">
         <v>100203</v>
       </c>
-      <c r="J82" s="6">
-        <v>0</v>
-      </c>
       <c r="K82" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="6">
         <v>1</v>
       </c>
       <c r="M82" s="6">
+        <v>1</v>
+      </c>
+      <c r="N82" s="6">
         <v>20</v>
       </c>
-      <c r="N82" s="6">
-        <v>0</v>
-      </c>
       <c r="O82" s="6">
         <v>0</v>
       </c>
       <c r="P82" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="7"/>
       <c r="C83" s="6">
         <v>3102</v>
@@ -6145,44 +6637,47 @@
       <c r="D83" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E83" s="6">
-        <v>0</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G83" s="6">
-        <v>0</v>
+      <c r="E83" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F83" s="6">
+        <v>0</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H83" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" s="6">
+        <v>1</v>
+      </c>
+      <c r="J83" s="6">
         <v>100403</v>
       </c>
-      <c r="J83" s="6">
-        <v>0</v>
-      </c>
       <c r="K83" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="6">
         <v>1</v>
       </c>
       <c r="M83" s="6">
+        <v>1</v>
+      </c>
+      <c r="N83" s="6">
         <v>20</v>
       </c>
-      <c r="N83" s="6">
-        <v>0</v>
-      </c>
       <c r="O83" s="6">
         <v>0</v>
       </c>
       <c r="P83" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="7"/>
       <c r="C84" s="6">
         <v>3103</v>
@@ -6190,44 +6685,47 @@
       <c r="D84" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E84" s="6">
-        <v>0</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84" s="6">
-        <v>0</v>
+      <c r="E84" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F84" s="6">
+        <v>0</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H84" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" s="6">
+        <v>1</v>
+      </c>
+      <c r="J84" s="6">
         <v>100603</v>
       </c>
-      <c r="J84" s="6">
-        <v>0</v>
-      </c>
       <c r="K84" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="6">
         <v>1</v>
       </c>
       <c r="M84" s="6">
+        <v>1</v>
+      </c>
+      <c r="N84" s="6">
         <v>20</v>
       </c>
-      <c r="N84" s="6">
-        <v>0</v>
-      </c>
       <c r="O84" s="6">
         <v>0</v>
       </c>
       <c r="P84" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="7"/>
       <c r="C85" s="6">
         <v>3104</v>
@@ -6235,44 +6733,47 @@
       <c r="D85" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E85" s="6">
-        <v>0</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G85" s="6">
-        <v>0</v>
+      <c r="E85" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F85" s="6">
+        <v>0</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H85" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" s="6">
+        <v>1</v>
+      </c>
+      <c r="J85" s="6">
         <v>100803</v>
       </c>
-      <c r="J85" s="6">
-        <v>0</v>
-      </c>
       <c r="K85" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="6">
         <v>1</v>
       </c>
       <c r="M85" s="6">
+        <v>1</v>
+      </c>
+      <c r="N85" s="6">
         <v>20</v>
       </c>
-      <c r="N85" s="6">
-        <v>0</v>
-      </c>
       <c r="O85" s="6">
         <v>0</v>
       </c>
       <c r="P85" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="7"/>
       <c r="C86" s="6">
         <v>3105</v>
@@ -6280,44 +6781,47 @@
       <c r="D86" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E86" s="6">
-        <v>0</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G86" s="6">
-        <v>0</v>
+      <c r="E86" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F86" s="6">
+        <v>0</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H86" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="6">
+        <v>1</v>
+      </c>
+      <c r="J86" s="6">
         <v>101003</v>
       </c>
-      <c r="J86" s="6">
-        <v>0</v>
-      </c>
       <c r="K86" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="6">
         <v>1</v>
       </c>
       <c r="M86" s="6">
+        <v>1</v>
+      </c>
+      <c r="N86" s="6">
         <v>40</v>
       </c>
-      <c r="N86" s="6">
-        <v>0</v>
-      </c>
       <c r="O86" s="6">
         <v>0</v>
       </c>
       <c r="P86" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="7"/>
       <c r="C87" s="6">
         <v>3201</v>
@@ -6325,44 +6829,47 @@
       <c r="D87" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E87" s="6">
-        <v>0</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G87" s="6">
-        <v>0</v>
+      <c r="E87" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F87" s="6">
+        <v>0</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H87" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="6">
+        <v>1</v>
+      </c>
+      <c r="J87" s="6">
         <v>100203</v>
       </c>
-      <c r="J87" s="6">
-        <v>0</v>
-      </c>
       <c r="K87" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="6">
         <v>1</v>
       </c>
       <c r="M87" s="6">
+        <v>1</v>
+      </c>
+      <c r="N87" s="6">
         <v>40</v>
       </c>
-      <c r="N87" s="6">
-        <v>0</v>
-      </c>
       <c r="O87" s="6">
         <v>0</v>
       </c>
       <c r="P87" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="7"/>
       <c r="C88" s="6">
         <v>3202</v>
@@ -6370,44 +6877,47 @@
       <c r="D88" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E88" s="6">
-        <v>0</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G88" s="6">
-        <v>0</v>
+      <c r="E88" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F88" s="6">
+        <v>0</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H88" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" s="6">
+        <v>1</v>
+      </c>
+      <c r="J88" s="6">
         <v>100403</v>
       </c>
-      <c r="J88" s="6">
-        <v>0</v>
-      </c>
       <c r="K88" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="6">
         <v>1</v>
       </c>
       <c r="M88" s="6">
+        <v>1</v>
+      </c>
+      <c r="N88" s="6">
         <v>40</v>
       </c>
-      <c r="N88" s="6">
-        <v>0</v>
-      </c>
       <c r="O88" s="6">
         <v>0</v>
       </c>
       <c r="P88" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="7"/>
       <c r="C89" s="6">
         <v>3203</v>
@@ -6415,44 +6925,47 @@
       <c r="D89" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E89" s="6">
-        <v>0</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" s="6">
-        <v>0</v>
+      <c r="E89" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F89" s="6">
+        <v>0</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H89" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" s="6">
+        <v>1</v>
+      </c>
+      <c r="J89" s="6">
         <v>100603</v>
       </c>
-      <c r="J89" s="6">
-        <v>0</v>
-      </c>
       <c r="K89" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="6">
         <v>1</v>
       </c>
       <c r="M89" s="6">
+        <v>1</v>
+      </c>
+      <c r="N89" s="6">
         <v>40</v>
       </c>
-      <c r="N89" s="6">
-        <v>0</v>
-      </c>
       <c r="O89" s="6">
         <v>0</v>
       </c>
       <c r="P89" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B90" s="7"/>
       <c r="C90" s="6">
         <v>3204</v>
@@ -6460,44 +6973,47 @@
       <c r="D90" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E90" s="6">
-        <v>0</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G90" s="6">
-        <v>0</v>
+      <c r="E90" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F90" s="6">
+        <v>0</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H90" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="6">
+        <v>1</v>
+      </c>
+      <c r="J90" s="6">
         <v>100803</v>
       </c>
-      <c r="J90" s="6">
-        <v>0</v>
-      </c>
       <c r="K90" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" s="6">
         <v>1</v>
       </c>
       <c r="M90" s="6">
+        <v>1</v>
+      </c>
+      <c r="N90" s="6">
         <v>40</v>
       </c>
-      <c r="N90" s="6">
-        <v>0</v>
-      </c>
       <c r="O90" s="6">
         <v>0</v>
       </c>
       <c r="P90" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B91" s="7"/>
       <c r="C91" s="6">
         <v>3205</v>
@@ -6505,44 +7021,47 @@
       <c r="D91" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E91" s="6">
-        <v>0</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G91" s="6">
-        <v>0</v>
+      <c r="E91" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F91" s="6">
+        <v>0</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H91" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" s="6">
+        <v>1</v>
+      </c>
+      <c r="J91" s="6">
         <v>101003</v>
       </c>
-      <c r="J91" s="6">
-        <v>0</v>
-      </c>
       <c r="K91" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="6">
         <v>1</v>
       </c>
       <c r="M91" s="6">
+        <v>1</v>
+      </c>
+      <c r="N91" s="6">
         <v>80</v>
       </c>
-      <c r="N91" s="6">
-        <v>0</v>
-      </c>
       <c r="O91" s="6">
         <v>0</v>
       </c>
       <c r="P91" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B92" s="7"/>
       <c r="C92" s="6">
         <v>3301</v>
@@ -6550,44 +7069,47 @@
       <c r="D92" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E92" s="6">
-        <v>0</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G92" s="6">
-        <v>0</v>
+      <c r="E92" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F92" s="6">
+        <v>0</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H92" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" s="6">
+        <v>1</v>
+      </c>
+      <c r="J92" s="6">
         <v>100203</v>
       </c>
-      <c r="J92" s="6">
-        <v>0</v>
-      </c>
       <c r="K92" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="6">
         <v>1</v>
       </c>
       <c r="M92" s="6">
+        <v>1</v>
+      </c>
+      <c r="N92" s="6">
         <v>60</v>
       </c>
-      <c r="N92" s="6">
-        <v>0</v>
-      </c>
       <c r="O92" s="6">
         <v>0</v>
       </c>
       <c r="P92" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B93" s="7"/>
       <c r="C93" s="6">
         <v>3302</v>
@@ -6595,44 +7117,47 @@
       <c r="D93" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E93" s="6">
-        <v>0</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G93" s="6">
-        <v>0</v>
+      <c r="E93" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F93" s="6">
+        <v>0</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H93" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" s="6">
+        <v>1</v>
+      </c>
+      <c r="J93" s="6">
         <v>100403</v>
       </c>
-      <c r="J93" s="6">
-        <v>0</v>
-      </c>
       <c r="K93" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="6">
         <v>1</v>
       </c>
       <c r="M93" s="6">
+        <v>1</v>
+      </c>
+      <c r="N93" s="6">
         <v>60</v>
       </c>
-      <c r="N93" s="6">
-        <v>0</v>
-      </c>
       <c r="O93" s="6">
         <v>0</v>
       </c>
       <c r="P93" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B94" s="7"/>
       <c r="C94" s="6">
         <v>3303</v>
@@ -6640,44 +7165,47 @@
       <c r="D94" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E94" s="6">
-        <v>0</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="6">
-        <v>0</v>
+      <c r="E94" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F94" s="6">
+        <v>0</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H94" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" s="6">
+        <v>1</v>
+      </c>
+      <c r="J94" s="6">
         <v>100603</v>
       </c>
-      <c r="J94" s="6">
-        <v>0</v>
-      </c>
       <c r="K94" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="6">
         <v>1</v>
       </c>
       <c r="M94" s="6">
+        <v>1</v>
+      </c>
+      <c r="N94" s="6">
         <v>60</v>
       </c>
-      <c r="N94" s="6">
-        <v>0</v>
-      </c>
       <c r="O94" s="6">
         <v>0</v>
       </c>
       <c r="P94" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B95" s="7"/>
       <c r="C95" s="6">
         <v>3304</v>
@@ -6685,44 +7213,47 @@
       <c r="D95" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E95" s="6">
-        <v>0</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G95" s="6">
-        <v>0</v>
+      <c r="E95" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F95" s="6">
+        <v>0</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H95" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" s="6">
+        <v>1</v>
+      </c>
+      <c r="J95" s="6">
         <v>100803</v>
       </c>
-      <c r="J95" s="6">
-        <v>0</v>
-      </c>
       <c r="K95" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="6">
         <v>1</v>
       </c>
       <c r="M95" s="6">
+        <v>1</v>
+      </c>
+      <c r="N95" s="6">
         <v>60</v>
       </c>
-      <c r="N95" s="6">
-        <v>0</v>
-      </c>
       <c r="O95" s="6">
         <v>0</v>
       </c>
       <c r="P95" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B96" s="7"/>
       <c r="C96" s="6">
         <v>3305</v>
@@ -6730,44 +7261,47 @@
       <c r="D96" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E96" s="6">
-        <v>0</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G96" s="6">
-        <v>0</v>
+      <c r="E96" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F96" s="6">
+        <v>0</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H96" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" s="6">
+        <v>1</v>
+      </c>
+      <c r="J96" s="6">
         <v>101003</v>
       </c>
-      <c r="J96" s="6">
-        <v>0</v>
-      </c>
       <c r="K96" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="6">
         <v>1</v>
       </c>
       <c r="M96" s="6">
+        <v>1</v>
+      </c>
+      <c r="N96" s="6">
         <v>120</v>
       </c>
-      <c r="N96" s="6">
-        <v>0</v>
-      </c>
       <c r="O96" s="6">
         <v>0</v>
       </c>
       <c r="P96" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B97" s="7"/>
       <c r="C97" s="6">
         <v>3401</v>
@@ -6775,44 +7309,47 @@
       <c r="D97" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E97" s="6">
-        <v>0</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G97" s="6">
-        <v>0</v>
+      <c r="E97" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F97" s="6">
+        <v>0</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H97" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97" s="6">
+        <v>1</v>
+      </c>
+      <c r="J97" s="6">
         <v>100203</v>
       </c>
-      <c r="J97" s="6">
-        <v>0</v>
-      </c>
       <c r="K97" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="6">
         <v>1</v>
       </c>
       <c r="M97" s="6">
+        <v>1</v>
+      </c>
+      <c r="N97" s="6">
         <v>80</v>
       </c>
-      <c r="N97" s="6">
-        <v>0</v>
-      </c>
       <c r="O97" s="6">
         <v>0</v>
       </c>
       <c r="P97" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B98" s="7"/>
       <c r="C98" s="6">
         <v>3402</v>
@@ -6820,44 +7357,47 @@
       <c r="D98" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E98" s="6">
-        <v>0</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G98" s="6">
-        <v>0</v>
+      <c r="E98" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F98" s="6">
+        <v>0</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H98" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I98" s="6">
+        <v>1</v>
+      </c>
+      <c r="J98" s="6">
         <v>100403</v>
       </c>
-      <c r="J98" s="6">
-        <v>0</v>
-      </c>
       <c r="K98" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="6">
         <v>1</v>
       </c>
       <c r="M98" s="6">
+        <v>1</v>
+      </c>
+      <c r="N98" s="6">
         <v>80</v>
       </c>
-      <c r="N98" s="6">
-        <v>0</v>
-      </c>
       <c r="O98" s="6">
         <v>0</v>
       </c>
       <c r="P98" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B99" s="7"/>
       <c r="C99" s="6">
         <v>3403</v>
@@ -6865,44 +7405,47 @@
       <c r="D99" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E99" s="6">
-        <v>0</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G99" s="6">
-        <v>0</v>
+      <c r="E99" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F99" s="6">
+        <v>0</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H99" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" s="6">
+        <v>1</v>
+      </c>
+      <c r="J99" s="6">
         <v>100603</v>
       </c>
-      <c r="J99" s="6">
-        <v>0</v>
-      </c>
       <c r="K99" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="6">
         <v>1</v>
       </c>
       <c r="M99" s="6">
+        <v>1</v>
+      </c>
+      <c r="N99" s="6">
         <v>80</v>
       </c>
-      <c r="N99" s="6">
-        <v>0</v>
-      </c>
       <c r="O99" s="6">
         <v>0</v>
       </c>
       <c r="P99" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B100" s="7"/>
       <c r="C100" s="6">
         <v>3404</v>
@@ -6910,44 +7453,47 @@
       <c r="D100" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E100" s="6">
-        <v>0</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G100" s="6">
-        <v>0</v>
+      <c r="E100" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F100" s="6">
+        <v>0</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H100" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I100" s="6">
+        <v>1</v>
+      </c>
+      <c r="J100" s="6">
         <v>100803</v>
       </c>
-      <c r="J100" s="6">
-        <v>0</v>
-      </c>
       <c r="K100" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="6">
         <v>1</v>
       </c>
       <c r="M100" s="6">
+        <v>1</v>
+      </c>
+      <c r="N100" s="6">
         <v>80</v>
       </c>
-      <c r="N100" s="6">
-        <v>0</v>
-      </c>
       <c r="O100" s="6">
         <v>0</v>
       </c>
       <c r="P100" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B101" s="7"/>
       <c r="C101" s="6">
         <v>3405</v>
@@ -6955,44 +7501,47 @@
       <c r="D101" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E101" s="6">
-        <v>0</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G101" s="6">
-        <v>0</v>
+      <c r="E101" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F101" s="6">
+        <v>0</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H101" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" s="6">
+        <v>1</v>
+      </c>
+      <c r="J101" s="6">
         <v>101003</v>
       </c>
-      <c r="J101" s="6">
-        <v>0</v>
-      </c>
       <c r="K101" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="6">
         <v>1</v>
       </c>
       <c r="M101" s="6">
+        <v>1</v>
+      </c>
+      <c r="N101" s="6">
         <v>160</v>
       </c>
-      <c r="N101" s="6">
-        <v>0</v>
-      </c>
       <c r="O101" s="6">
         <v>0</v>
       </c>
       <c r="P101" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B102" s="7"/>
       <c r="C102" s="6">
         <v>3501</v>
@@ -7000,44 +7549,47 @@
       <c r="D102" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E102" s="6">
-        <v>0</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G102" s="6">
-        <v>0</v>
+      <c r="E102" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F102" s="6">
+        <v>0</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H102" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="6">
+        <v>1</v>
+      </c>
+      <c r="J102" s="6">
         <v>100203</v>
       </c>
-      <c r="J102" s="6">
-        <v>0</v>
-      </c>
       <c r="K102" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="6">
         <v>1</v>
       </c>
       <c r="M102" s="6">
+        <v>1</v>
+      </c>
+      <c r="N102" s="6">
         <v>100</v>
       </c>
-      <c r="N102" s="6">
-        <v>0</v>
-      </c>
       <c r="O102" s="6">
         <v>0</v>
       </c>
       <c r="P102" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B103" s="7"/>
       <c r="C103" s="6">
         <v>3502</v>
@@ -7045,44 +7597,47 @@
       <c r="D103" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E103" s="6">
-        <v>0</v>
-      </c>
-      <c r="F103" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G103" s="6">
-        <v>0</v>
+      <c r="E103" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F103" s="6">
+        <v>0</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H103" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" s="6">
+        <v>1</v>
+      </c>
+      <c r="J103" s="6">
         <v>100403</v>
       </c>
-      <c r="J103" s="6">
-        <v>0</v>
-      </c>
       <c r="K103" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="6">
         <v>1</v>
       </c>
       <c r="M103" s="6">
+        <v>1</v>
+      </c>
+      <c r="N103" s="6">
         <v>100</v>
       </c>
-      <c r="N103" s="6">
-        <v>0</v>
-      </c>
       <c r="O103" s="6">
         <v>0</v>
       </c>
       <c r="P103" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B104" s="7"/>
       <c r="C104" s="6">
         <v>3503</v>
@@ -7090,44 +7645,47 @@
       <c r="D104" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E104" s="6">
-        <v>0</v>
-      </c>
-      <c r="F104" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G104" s="6">
-        <v>0</v>
+      <c r="E104" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F104" s="6">
+        <v>0</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H104" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" s="6">
+        <v>1</v>
+      </c>
+      <c r="J104" s="6">
         <v>100603</v>
       </c>
-      <c r="J104" s="6">
-        <v>0</v>
-      </c>
       <c r="K104" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="6">
         <v>1</v>
       </c>
       <c r="M104" s="6">
+        <v>1</v>
+      </c>
+      <c r="N104" s="6">
         <v>100</v>
       </c>
-      <c r="N104" s="6">
-        <v>0</v>
-      </c>
       <c r="O104" s="6">
         <v>0</v>
       </c>
       <c r="P104" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B105" s="7"/>
       <c r="C105" s="6">
         <v>3504</v>
@@ -7135,44 +7693,47 @@
       <c r="D105" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E105" s="6">
-        <v>0</v>
-      </c>
-      <c r="F105" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G105" s="6">
-        <v>0</v>
+      <c r="E105" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F105" s="6">
+        <v>0</v>
+      </c>
+      <c r="G105" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H105" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="6">
+        <v>1</v>
+      </c>
+      <c r="J105" s="6">
         <v>100803</v>
       </c>
-      <c r="J105" s="6">
-        <v>0</v>
-      </c>
       <c r="K105" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="6">
         <v>1</v>
       </c>
       <c r="M105" s="6">
+        <v>1</v>
+      </c>
+      <c r="N105" s="6">
         <v>100</v>
       </c>
-      <c r="N105" s="6">
-        <v>0</v>
-      </c>
       <c r="O105" s="6">
         <v>0</v>
       </c>
       <c r="P105" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B106" s="7"/>
       <c r="C106" s="6">
         <v>3505</v>
@@ -7180,44 +7741,47 @@
       <c r="D106" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E106" s="6">
-        <v>0</v>
-      </c>
-      <c r="F106" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G106" s="6">
-        <v>0</v>
+      <c r="E106" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F106" s="6">
+        <v>0</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H106" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="6">
+        <v>1</v>
+      </c>
+      <c r="J106" s="6">
         <v>101003</v>
       </c>
-      <c r="J106" s="6">
-        <v>0</v>
-      </c>
       <c r="K106" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="6">
         <v>1</v>
       </c>
       <c r="M106" s="6">
+        <v>1</v>
+      </c>
+      <c r="N106" s="6">
         <v>200</v>
       </c>
-      <c r="N106" s="6">
-        <v>0</v>
-      </c>
       <c r="O106" s="6">
         <v>0</v>
       </c>
       <c r="P106" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B107" s="7"/>
       <c r="C107" s="6">
         <v>3601</v>
@@ -7225,44 +7789,47 @@
       <c r="D107" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E107" s="6">
-        <v>0</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G107" s="6">
-        <v>0</v>
+      <c r="E107" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F107" s="6">
+        <v>0</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H107" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107" s="6">
+        <v>1</v>
+      </c>
+      <c r="J107" s="6">
         <v>100203</v>
       </c>
-      <c r="J107" s="6">
-        <v>0</v>
-      </c>
       <c r="K107" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="6">
         <v>1</v>
       </c>
       <c r="M107" s="6">
+        <v>1</v>
+      </c>
+      <c r="N107" s="6">
         <v>120</v>
       </c>
-      <c r="N107" s="6">
-        <v>0</v>
-      </c>
       <c r="O107" s="6">
         <v>0</v>
       </c>
       <c r="P107" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B108" s="7"/>
       <c r="C108" s="6">
         <v>3602</v>
@@ -7270,44 +7837,47 @@
       <c r="D108" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E108" s="6">
-        <v>0</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G108" s="6">
-        <v>0</v>
+      <c r="E108" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F108" s="6">
+        <v>0</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H108" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="6">
+        <v>1</v>
+      </c>
+      <c r="J108" s="6">
         <v>100403</v>
       </c>
-      <c r="J108" s="6">
-        <v>0</v>
-      </c>
       <c r="K108" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="6">
         <v>1</v>
       </c>
       <c r="M108" s="6">
+        <v>1</v>
+      </c>
+      <c r="N108" s="6">
         <v>120</v>
       </c>
-      <c r="N108" s="6">
-        <v>0</v>
-      </c>
       <c r="O108" s="6">
         <v>0</v>
       </c>
       <c r="P108" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B109" s="7"/>
       <c r="C109" s="6">
         <v>3603</v>
@@ -7315,44 +7885,47 @@
       <c r="D109" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E109" s="6">
-        <v>0</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G109" s="6">
-        <v>0</v>
+      <c r="E109" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F109" s="6">
+        <v>0</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H109" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="6">
+        <v>1</v>
+      </c>
+      <c r="J109" s="6">
         <v>100603</v>
       </c>
-      <c r="J109" s="6">
-        <v>0</v>
-      </c>
       <c r="K109" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="6">
         <v>1</v>
       </c>
       <c r="M109" s="6">
+        <v>1</v>
+      </c>
+      <c r="N109" s="6">
         <v>120</v>
       </c>
-      <c r="N109" s="6">
-        <v>0</v>
-      </c>
       <c r="O109" s="6">
         <v>0</v>
       </c>
       <c r="P109" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B110" s="7"/>
       <c r="C110" s="6">
         <v>3604</v>
@@ -7360,44 +7933,47 @@
       <c r="D110" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E110" s="6">
-        <v>0</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G110" s="6">
-        <v>0</v>
+      <c r="E110" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F110" s="6">
+        <v>0</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H110" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="6">
+        <v>1</v>
+      </c>
+      <c r="J110" s="6">
         <v>100803</v>
       </c>
-      <c r="J110" s="6">
-        <v>0</v>
-      </c>
       <c r="K110" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="6">
         <v>1</v>
       </c>
       <c r="M110" s="6">
+        <v>1</v>
+      </c>
+      <c r="N110" s="6">
         <v>120</v>
       </c>
-      <c r="N110" s="6">
-        <v>0</v>
-      </c>
       <c r="O110" s="6">
         <v>0</v>
       </c>
       <c r="P110" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B111" s="7"/>
       <c r="C111" s="6">
         <v>3605</v>
@@ -7405,70 +7981,73 @@
       <c r="D111" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E111" s="6">
-        <v>0</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G111" s="6">
-        <v>0</v>
+      <c r="E111" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F111" s="6">
+        <v>0</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H111" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" s="6">
+        <v>1</v>
+      </c>
+      <c r="J111" s="6">
         <v>101003</v>
       </c>
-      <c r="J111" s="6">
-        <v>0</v>
-      </c>
       <c r="K111" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="6">
         <v>1</v>
       </c>
       <c r="M111" s="6">
+        <v>1</v>
+      </c>
+      <c r="N111" s="6">
         <v>240</v>
       </c>
-      <c r="N111" s="6">
-        <v>0</v>
-      </c>
       <c r="O111" s="6">
         <v>0</v>
       </c>
       <c r="P111" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C112" s="6">
         <v>3901</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E112" s="6">
+      <c r="E112" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F112" s="6">
         <v>1013</v>
       </c>
-      <c r="F112" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G112" s="6">
-        <v>0</v>
+      <c r="G112" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H112" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" s="6">
+        <v>1</v>
+      </c>
+      <c r="J112" s="6">
         <v>120101</v>
       </c>
-      <c r="J112" s="6">
-        <v>0</v>
-      </c>
       <c r="K112" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" s="6">
         <v>1</v>
@@ -7477,40 +8056,43 @@
         <v>1</v>
       </c>
       <c r="N112" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P112" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q112" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C113" s="6">
         <v>3902</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E113" s="6">
+      <c r="E113" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F113" s="6">
         <v>2109</v>
       </c>
-      <c r="F113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G113" s="6">
-        <v>0</v>
+      <c r="G113" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H113" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" s="6">
+        <v>1</v>
+      </c>
+      <c r="J113" s="6">
         <v>68000108</v>
       </c>
-      <c r="J113" s="6">
-        <v>0</v>
-      </c>
       <c r="K113" s="6">
         <v>0</v>
       </c>
@@ -7524,37 +8106,40 @@
         <v>0</v>
       </c>
       <c r="O113" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P113" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q113" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C114" s="6">
         <v>3903</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E114" s="6">
+      <c r="E114" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F114" s="6">
         <v>2105</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G114" s="6">
-        <v>0</v>
+      <c r="G114" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H114" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" s="6">
+        <v>1</v>
+      </c>
+      <c r="J114" s="6">
         <v>68000104</v>
       </c>
-      <c r="J114" s="6">
-        <v>0</v>
-      </c>
       <c r="K114" s="6">
         <v>0</v>
       </c>
@@ -7568,37 +8153,40 @@
         <v>0</v>
       </c>
       <c r="O114" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P114" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q114" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C115" s="6">
         <v>3904</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E115" s="6">
+      <c r="E115" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F115" s="6">
         <v>2106</v>
       </c>
-      <c r="F115" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G115" s="6">
-        <v>0</v>
+      <c r="G115" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H115" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" s="6">
+        <v>1</v>
+      </c>
+      <c r="J115" s="6">
         <v>68000105</v>
       </c>
-      <c r="J115" s="6">
-        <v>0</v>
-      </c>
       <c r="K115" s="6">
         <v>0</v>
       </c>
@@ -7612,13 +8200,16 @@
         <v>0</v>
       </c>
       <c r="O115" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P115" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q115" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B116" s="7"/>
       <c r="C116" s="6">
         <v>3905</v>
@@ -7626,288 +8217,306 @@
       <c r="D116" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E116" s="6">
-        <v>0</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G116" s="6">
-        <v>0</v>
+      <c r="E116" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F116" s="6">
+        <v>0</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H116" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I116" s="6">
+        <v>1</v>
+      </c>
+      <c r="J116" s="6">
         <v>100403</v>
       </c>
-      <c r="J116" s="6">
-        <v>0</v>
-      </c>
       <c r="K116" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="6">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M116" s="6">
         <v>120</v>
       </c>
       <c r="N116" s="6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O116" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P116" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q116" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C117" s="6">
         <v>3906</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E117" s="6">
+      <c r="E117" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F117" s="6">
         <v>1018</v>
       </c>
-      <c r="F117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G117" s="6">
-        <v>0</v>
+      <c r="G117" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H117" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I117" s="6">
+        <v>1</v>
+      </c>
+      <c r="J117" s="6">
         <v>200101</v>
       </c>
-      <c r="J117" s="6">
-        <v>0</v>
-      </c>
       <c r="K117" s="6">
         <v>0</v>
       </c>
       <c r="L117" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M117" s="6">
         <v>0.02</v>
       </c>
       <c r="N117" s="6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O117" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P117" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q117" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C118" s="6">
         <v>3907</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E118" s="6">
+      <c r="E118" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F118" s="6">
         <v>1019</v>
       </c>
-      <c r="F118" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G118" s="6">
-        <v>0</v>
+      <c r="G118" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H118" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="6">
+        <v>1</v>
+      </c>
+      <c r="J118" s="6">
         <v>200201</v>
       </c>
-      <c r="J118" s="6">
-        <v>0</v>
-      </c>
       <c r="K118" s="6">
         <v>0</v>
       </c>
       <c r="L118" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M118" s="6">
         <v>0.02</v>
       </c>
       <c r="N118" s="6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O118" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P118" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q118" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C119" s="6">
         <v>3908</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E119" s="6">
+      <c r="E119" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F119" s="6">
         <v>1020</v>
       </c>
-      <c r="F119" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G119" s="6">
-        <v>0</v>
+      <c r="G119" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H119" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="6">
+        <v>1</v>
+      </c>
+      <c r="J119" s="6">
         <v>200301</v>
       </c>
-      <c r="J119" s="6">
-        <v>0</v>
-      </c>
       <c r="K119" s="6">
         <v>0</v>
       </c>
       <c r="L119" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M119" s="6">
         <v>0.02</v>
       </c>
       <c r="N119" s="6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O119" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P119" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q119" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C120" s="6">
         <v>3909</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E120" s="6">
+      <c r="E120" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F120" s="6">
         <v>1021</v>
       </c>
-      <c r="F120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G120" s="6">
-        <v>0</v>
+      <c r="G120" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H120" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="6">
+        <v>1</v>
+      </c>
+      <c r="J120" s="6">
         <v>200401</v>
       </c>
-      <c r="J120" s="6">
-        <v>0</v>
-      </c>
       <c r="K120" s="6">
         <v>0</v>
       </c>
       <c r="L120" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M120" s="6">
         <v>0.02</v>
       </c>
       <c r="N120" s="6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O120" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P120" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q120" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C121" s="6">
         <v>3910</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E121" s="6">
+      <c r="E121" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F121" s="6">
         <v>1008</v>
       </c>
-      <c r="F121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G121" s="6">
-        <v>0</v>
+      <c r="G121" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="H121" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" s="6">
+        <v>1</v>
+      </c>
+      <c r="J121" s="6">
         <v>202101</v>
       </c>
-      <c r="J121" s="6">
-        <v>0</v>
-      </c>
       <c r="K121" s="6">
         <v>0</v>
       </c>
       <c r="L121" s="6">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="M121" s="6">
         <v>0.02</v>
       </c>
       <c r="N121" s="6">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O121" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P121" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q121" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C122" s="6">
         <v>10001</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E122" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F122" s="6">
         <v>10002</v>
       </c>
-      <c r="F122" s="9" t="s">
+      <c r="G122" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G122" s="6">
-        <v>0</v>
-      </c>
       <c r="H122" s="6">
+        <v>0</v>
+      </c>
+      <c r="I122" s="6">
         <v>0.15</v>
       </c>
-      <c r="I122" s="6">
+      <c r="J122" s="6">
         <v>105101</v>
       </c>
-      <c r="J122" s="6">
-        <v>1</v>
-      </c>
       <c r="K122" s="6">
         <v>1</v>
       </c>
@@ -7915,43 +8524,46 @@
         <v>1</v>
       </c>
       <c r="M122" s="6">
+        <v>1</v>
+      </c>
+      <c r="N122" s="6">
         <v>5</v>
       </c>
-      <c r="N122" s="6">
-        <v>0</v>
-      </c>
       <c r="O122" s="6">
         <v>0</v>
       </c>
       <c r="P122" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q122" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C123" s="6">
         <v>10002</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E123" s="6">
+      <c r="E123" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F123" s="6">
         <v>10003</v>
       </c>
-      <c r="F123" s="9" t="s">
+      <c r="G123" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G123" s="6">
-        <v>0</v>
-      </c>
       <c r="H123" s="6">
+        <v>0</v>
+      </c>
+      <c r="I123" s="6">
         <v>0.15</v>
       </c>
-      <c r="I123" s="6">
+      <c r="J123" s="6">
         <v>105301</v>
       </c>
-      <c r="J123" s="6">
-        <v>1</v>
-      </c>
       <c r="K123" s="6">
         <v>1</v>
       </c>
@@ -7959,43 +8571,46 @@
         <v>1</v>
       </c>
       <c r="M123" s="6">
+        <v>1</v>
+      </c>
+      <c r="N123" s="6">
         <v>5</v>
       </c>
-      <c r="N123" s="6">
-        <v>0</v>
-      </c>
       <c r="O123" s="6">
         <v>0</v>
       </c>
       <c r="P123" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q123" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C124" s="6">
         <v>10003</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E124" s="6">
+      <c r="E124" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F124" s="6">
         <v>10004</v>
       </c>
-      <c r="F124" s="9" t="s">
+      <c r="G124" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G124" s="6">
-        <v>0</v>
-      </c>
       <c r="H124" s="6">
+        <v>0</v>
+      </c>
+      <c r="I124" s="6">
         <v>0.16</v>
       </c>
-      <c r="I124" s="6">
+      <c r="J124" s="6">
         <v>105501</v>
       </c>
-      <c r="J124" s="6">
-        <v>1</v>
-      </c>
       <c r="K124" s="6">
         <v>1</v>
       </c>
@@ -8003,43 +8618,46 @@
         <v>1</v>
       </c>
       <c r="M124" s="6">
+        <v>1</v>
+      </c>
+      <c r="N124" s="6">
         <v>5</v>
       </c>
-      <c r="N124" s="6">
-        <v>0</v>
-      </c>
       <c r="O124" s="6">
         <v>0</v>
       </c>
       <c r="P124" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="2:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C125" s="6">
         <v>10004</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E125" s="6">
+      <c r="E125" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F125" s="6">
         <v>10005</v>
       </c>
-      <c r="F125" s="9" t="s">
+      <c r="G125" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G125" s="6">
-        <v>0</v>
-      </c>
       <c r="H125" s="6">
+        <v>0</v>
+      </c>
+      <c r="I125" s="6">
         <v>0.15</v>
       </c>
-      <c r="I125" s="6">
+      <c r="J125" s="6">
         <v>105401</v>
       </c>
-      <c r="J125" s="6">
-        <v>1</v>
-      </c>
       <c r="K125" s="6">
         <v>1</v>
       </c>
@@ -8047,599 +8665,641 @@
         <v>1</v>
       </c>
       <c r="M125" s="6">
+        <v>1</v>
+      </c>
+      <c r="N125" s="6">
         <v>5</v>
       </c>
-      <c r="N125" s="6">
-        <v>0</v>
-      </c>
       <c r="O125" s="6">
         <v>0</v>
       </c>
       <c r="P125" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C126" s="6">
         <v>10005</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E126" s="6">
+      <c r="E126" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F126" s="6">
         <v>10006</v>
       </c>
-      <c r="F126" s="9" t="s">
+      <c r="G126" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G126" s="6">
-        <v>0</v>
-      </c>
       <c r="H126" s="6">
+        <v>0</v>
+      </c>
+      <c r="I126" s="6">
         <v>0.03</v>
       </c>
-      <c r="I126" s="6">
+      <c r="J126" s="6">
         <v>200101</v>
       </c>
-      <c r="J126" s="6">
-        <v>1</v>
-      </c>
       <c r="K126" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="6">
+        <v>0</v>
+      </c>
+      <c r="M126" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M126" s="6">
+      <c r="N126" s="6">
         <v>0.01</v>
       </c>
-      <c r="N126" s="6">
-        <v>0</v>
-      </c>
       <c r="O126" s="6">
         <v>0</v>
       </c>
       <c r="P126" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C127" s="6">
         <v>10006</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E127" s="6">
+      <c r="E127" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F127" s="6">
         <v>10007</v>
       </c>
-      <c r="F127" s="9" t="s">
+      <c r="G127" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G127" s="6">
-        <v>0</v>
-      </c>
       <c r="H127" s="6">
+        <v>0</v>
+      </c>
+      <c r="I127" s="6">
         <v>0.03</v>
       </c>
-      <c r="I127" s="6">
+      <c r="J127" s="6">
         <v>200201</v>
       </c>
-      <c r="J127" s="6">
-        <v>1</v>
-      </c>
       <c r="K127" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="6">
+        <v>0</v>
+      </c>
+      <c r="M127" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M127" s="6">
+      <c r="N127" s="6">
         <v>0.01</v>
       </c>
-      <c r="N127" s="6">
-        <v>0</v>
-      </c>
       <c r="O127" s="6">
         <v>0</v>
       </c>
       <c r="P127" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="2:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C128" s="6">
         <v>10007</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E128" s="6">
+      <c r="E128" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F128" s="6">
         <v>10008</v>
       </c>
-      <c r="F128" s="9" t="s">
+      <c r="G128" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G128" s="6">
-        <v>0</v>
-      </c>
       <c r="H128" s="6">
+        <v>0</v>
+      </c>
+      <c r="I128" s="6">
         <v>0.03</v>
       </c>
-      <c r="I128" s="6">
+      <c r="J128" s="6">
         <v>200301</v>
       </c>
-      <c r="J128" s="6">
-        <v>1</v>
-      </c>
       <c r="K128" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="6">
+        <v>0</v>
+      </c>
+      <c r="M128" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M128" s="6">
+      <c r="N128" s="6">
         <v>0.01</v>
       </c>
-      <c r="N128" s="6">
-        <v>0</v>
-      </c>
       <c r="O128" s="6">
         <v>0</v>
       </c>
       <c r="P128" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C129" s="6">
         <v>10008</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E129" s="6">
+      <c r="E129" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F129" s="6">
         <v>10009</v>
       </c>
-      <c r="F129" s="9" t="s">
+      <c r="G129" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G129" s="6">
-        <v>0</v>
-      </c>
       <c r="H129" s="6">
+        <v>0</v>
+      </c>
+      <c r="I129" s="6">
         <v>0.03</v>
       </c>
-      <c r="I129" s="6">
+      <c r="J129" s="6">
         <v>200401</v>
       </c>
-      <c r="J129" s="6">
-        <v>1</v>
-      </c>
       <c r="K129" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="6">
+        <v>0</v>
+      </c>
+      <c r="M129" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M129" s="6">
+      <c r="N129" s="6">
         <v>0.01</v>
       </c>
-      <c r="N129" s="6">
-        <v>0</v>
-      </c>
       <c r="O129" s="6">
         <v>0</v>
       </c>
       <c r="P129" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="3:16" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C130" s="6">
         <v>10009</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E130" s="6">
+      <c r="E130" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F130" s="6">
         <v>10010</v>
       </c>
-      <c r="F130" s="9" t="s">
+      <c r="G130" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G130" s="6">
-        <v>0</v>
-      </c>
       <c r="H130" s="6">
+        <v>0</v>
+      </c>
+      <c r="I130" s="6">
         <v>0.03</v>
       </c>
-      <c r="I130" s="6">
+      <c r="J130" s="6">
         <v>202101</v>
       </c>
-      <c r="J130" s="6">
-        <v>1</v>
-      </c>
       <c r="K130" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="6">
+        <v>0</v>
+      </c>
+      <c r="M130" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M130" s="6">
+      <c r="N130" s="6">
         <v>0.01</v>
       </c>
-      <c r="N130" s="6">
-        <v>0</v>
-      </c>
       <c r="O130" s="6">
         <v>0</v>
       </c>
       <c r="P130" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C131" s="6">
         <v>10010</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E131" s="6">
+      <c r="E131" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F131" s="6">
         <v>10011</v>
       </c>
-      <c r="F131" s="9" t="s">
+      <c r="G131" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G131" s="6">
-        <v>0</v>
-      </c>
       <c r="H131" s="6">
+        <v>0</v>
+      </c>
+      <c r="I131" s="6">
         <v>0.03</v>
       </c>
-      <c r="I131" s="6">
+      <c r="J131" s="6">
         <v>200501</v>
       </c>
-      <c r="J131" s="6">
-        <v>1</v>
-      </c>
       <c r="K131" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="6">
+        <v>0</v>
+      </c>
+      <c r="M131" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M131" s="6">
+      <c r="N131" s="6">
         <v>0.01</v>
       </c>
-      <c r="N131" s="6">
-        <v>0</v>
-      </c>
       <c r="O131" s="6">
         <v>0</v>
       </c>
       <c r="P131" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C132" s="6">
         <v>10011</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E132" s="6">
+      <c r="E132" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F132" s="6">
         <v>10012</v>
       </c>
-      <c r="F132" s="9" t="s">
+      <c r="G132" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G132" s="6">
-        <v>0</v>
-      </c>
       <c r="H132" s="6">
+        <v>0</v>
+      </c>
+      <c r="I132" s="6">
         <v>0.03</v>
       </c>
-      <c r="I132" s="6">
+      <c r="J132" s="6">
         <v>200601</v>
       </c>
-      <c r="J132" s="6">
-        <v>1</v>
-      </c>
       <c r="K132" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="6">
+        <v>0</v>
+      </c>
+      <c r="M132" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M132" s="6">
+      <c r="N132" s="6">
         <v>0.01</v>
       </c>
-      <c r="N132" s="6">
-        <v>0</v>
-      </c>
       <c r="O132" s="6">
         <v>0</v>
       </c>
       <c r="P132" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q132" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C133" s="6">
         <v>10012</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E133" s="6">
+      <c r="E133" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F133" s="6">
         <v>10013</v>
       </c>
-      <c r="F133" s="9" t="s">
+      <c r="G133" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G133" s="6">
-        <v>0</v>
-      </c>
       <c r="H133" s="6">
+        <v>0</v>
+      </c>
+      <c r="I133" s="6">
         <v>0.03</v>
       </c>
-      <c r="I133" s="6">
+      <c r="J133" s="6">
         <v>200701</v>
       </c>
-      <c r="J133" s="6">
-        <v>1</v>
-      </c>
       <c r="K133" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="6">
+        <v>0</v>
+      </c>
+      <c r="M133" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M133" s="6">
+      <c r="N133" s="6">
         <v>0.01</v>
       </c>
-      <c r="N133" s="6">
-        <v>0</v>
-      </c>
       <c r="O133" s="6">
         <v>0</v>
       </c>
       <c r="P133" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q133" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C134" s="6">
         <v>10013</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E134" s="6">
+      <c r="E134" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F134" s="6">
         <v>10014</v>
       </c>
-      <c r="F134" s="9" t="s">
+      <c r="G134" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G134" s="6">
-        <v>0</v>
-      </c>
       <c r="H134" s="6">
+        <v>0</v>
+      </c>
+      <c r="I134" s="6">
         <v>0.03</v>
       </c>
-      <c r="I134" s="6">
+      <c r="J134" s="6">
         <v>200801</v>
       </c>
-      <c r="J134" s="6">
-        <v>1</v>
-      </c>
       <c r="K134" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="6">
+        <v>0</v>
+      </c>
+      <c r="M134" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M134" s="6">
+      <c r="N134" s="6">
         <v>0.01</v>
       </c>
-      <c r="N134" s="6">
-        <v>0</v>
-      </c>
       <c r="O134" s="6">
         <v>0</v>
       </c>
       <c r="P134" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q134" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C135" s="6">
         <v>10014</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E135" s="6">
+      <c r="E135" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F135" s="6">
         <v>10015</v>
       </c>
-      <c r="F135" s="9" t="s">
+      <c r="G135" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G135" s="6">
-        <v>0</v>
-      </c>
       <c r="H135" s="6">
+        <v>0</v>
+      </c>
+      <c r="I135" s="6">
         <v>0.03</v>
       </c>
-      <c r="I135" s="6">
+      <c r="J135" s="6">
         <v>200901</v>
       </c>
-      <c r="J135" s="6">
-        <v>1</v>
-      </c>
       <c r="K135" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" s="6">
+        <v>0</v>
+      </c>
+      <c r="M135" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M135" s="6">
+      <c r="N135" s="6">
         <v>0.01</v>
       </c>
-      <c r="N135" s="6">
-        <v>0</v>
-      </c>
       <c r="O135" s="6">
         <v>0</v>
       </c>
       <c r="P135" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C136" s="6">
         <v>10015</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E136" s="6">
+      <c r="E136" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F136" s="6">
         <v>10016</v>
       </c>
-      <c r="F136" s="9" t="s">
+      <c r="G136" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G136" s="6">
-        <v>0</v>
-      </c>
       <c r="H136" s="6">
+        <v>0</v>
+      </c>
+      <c r="I136" s="6">
         <v>0.03</v>
       </c>
-      <c r="I136" s="6">
+      <c r="J136" s="6">
         <v>201001</v>
       </c>
-      <c r="J136" s="6">
-        <v>1</v>
-      </c>
       <c r="K136" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="6">
+        <v>0</v>
+      </c>
+      <c r="M136" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M136" s="6">
+      <c r="N136" s="6">
         <v>0.01</v>
       </c>
-      <c r="N136" s="6">
-        <v>0</v>
-      </c>
       <c r="O136" s="6">
         <v>0</v>
       </c>
       <c r="P136" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q136" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C137" s="6">
         <v>10016</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E137" s="6">
+      <c r="E137" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F137" s="6">
         <v>10017</v>
       </c>
-      <c r="F137" s="9" t="s">
+      <c r="G137" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G137" s="6">
-        <v>0</v>
-      </c>
       <c r="H137" s="6">
+        <v>0</v>
+      </c>
+      <c r="I137" s="6">
         <v>0.03</v>
       </c>
-      <c r="I137" s="6">
+      <c r="J137" s="6">
         <v>202201</v>
       </c>
-      <c r="J137" s="6">
-        <v>1</v>
-      </c>
       <c r="K137" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" s="6">
+        <v>0</v>
+      </c>
+      <c r="M137" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M137" s="6">
+      <c r="N137" s="6">
         <v>0.01</v>
       </c>
-      <c r="N137" s="6">
-        <v>0</v>
-      </c>
       <c r="O137" s="6">
         <v>0</v>
       </c>
       <c r="P137" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C138" s="6">
         <v>10017</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E138" s="6">
-        <v>0</v>
-      </c>
-      <c r="F138" s="9" t="s">
+      <c r="E138" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F138" s="6">
+        <v>0</v>
+      </c>
+      <c r="G138" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G138" s="6">
-        <v>0</v>
-      </c>
       <c r="H138" s="6">
+        <v>0</v>
+      </c>
+      <c r="I138" s="6">
         <v>0.03</v>
       </c>
-      <c r="I138" s="6">
+      <c r="J138" s="6">
         <v>202301</v>
       </c>
-      <c r="J138" s="6">
-        <v>1</v>
-      </c>
       <c r="K138" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="6">
+        <v>0</v>
+      </c>
+      <c r="M138" s="6">
         <v>1E-3</v>
       </c>
-      <c r="M138" s="6">
+      <c r="N138" s="6">
         <v>0.01</v>
       </c>
-      <c r="N138" s="6">
-        <v>0</v>
-      </c>
       <c r="O138" s="6">
         <v>0</v>
       </c>
       <c r="P138" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C139" s="8">
         <v>30001</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E139" s="6">
-        <v>0</v>
+      <c r="E139" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="F139" s="6">
         <v>0</v>
@@ -8648,42 +9308,45 @@
         <v>0</v>
       </c>
       <c r="H139" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" s="6">
+        <v>1</v>
+      </c>
+      <c r="J139" s="6">
         <v>100403</v>
       </c>
-      <c r="J139" s="6">
-        <v>0</v>
-      </c>
       <c r="K139" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" s="6">
         <v>1</v>
       </c>
       <c r="M139" s="6">
+        <v>1</v>
+      </c>
+      <c r="N139" s="6">
         <v>5</v>
       </c>
-      <c r="N139" s="6">
-        <v>0</v>
-      </c>
       <c r="O139" s="6">
         <v>0</v>
       </c>
       <c r="P139" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="Q139" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C140" s="8">
         <v>40001</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E140" s="6">
-        <v>0</v>
+      <c r="E140" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="F140" s="6">
         <v>0</v>
@@ -8692,14 +9355,14 @@
         <v>0</v>
       </c>
       <c r="H140" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140" s="6">
+        <v>1</v>
+      </c>
+      <c r="J140" s="6">
         <v>68000104</v>
       </c>
-      <c r="J140" s="6">
-        <v>0</v>
-      </c>
       <c r="K140" s="6">
         <v>0</v>
       </c>
@@ -8713,16 +9376,19 @@
         <v>0</v>
       </c>
       <c r="O140" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P140" s="6">
+        <v>1</v>
+      </c>
+      <c r="Q140" s="6">
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" spans="3:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>

--- a/Excel/HideProListConfig.xlsx
+++ b/Excel/HideProListConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B1DA17-1651-4059-AD16-2C1D937F844C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D62FDC-5874-4BA8-B538-124FD794EB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HideProListProto" sheetId="1" r:id="rId1"/>
@@ -350,7 +350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="201">
   <si>
     <t>Id</t>
   </si>
@@ -712,66 +712,12 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Life</t>
-  </si>
-  <si>
     <t>Attack</t>
   </si>
   <si>
-    <t>Physical defense</t>
-  </si>
-  <si>
-    <t>Magic defense</t>
-  </si>
-  <si>
     <t>Block Value</t>
   </si>
   <si>
-    <t>Heavy Strike Additional Damage</t>
-  </si>
-  <si>
-    <t>Critical hit probability</t>
-  </si>
-  <si>
-    <t>True Damage</t>
-  </si>
-  <si>
-    <t>Recovery Value</t>
-  </si>
-  <si>
-    <t>Ignore the target's defense value.</t>
-  </si>
-  <si>
-    <t>Ignore the target's magic defense value</t>
-  </si>
-  <si>
-    <t>Lucky Value</t>
-  </si>
-  <si>
-    <t>Critical Strike Rating</t>
-  </si>
-  <si>
-    <t>Hit level</t>
-  </si>
-  <si>
-    <t>Dodge Level</t>
-  </si>
-  <si>
-    <t>Resistance to Aggression Level</t>
-  </si>
-  <si>
-    <t>Critical Hit Probability</t>
-  </si>
-  <si>
-    <t>Hit Chance</t>
-  </si>
-  <si>
-    <t>Evasion probability</t>
-  </si>
-  <si>
-    <t>Resistance to Damage Probability</t>
-  </si>
-  <si>
     <t>Physical damage</t>
   </si>
   <si>
@@ -790,66 +736,6 @@
     <t>Damage Reduction</t>
   </si>
   <si>
-    <t>Attack penetration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic Penetration  </t>
-  </si>
-  <si>
-    <t>Physical damage attack on the leader</t>
-  </si>
-  <si>
-    <t>Magical Damage to Lord in Attack</t>
-  </si>
-  <si>
-    <t>Lord's Physical Attack Reduction</t>
-  </si>
-  <si>
-    <t>Lord's magic attack reduction</t>
-  </si>
-  <si>
-    <t>Skill cooldown reduction</t>
-  </si>
-  <si>
-    <t>Experience bonus</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>Intelligence</t>
-  </si>
-  <si>
-    <t>Physique</t>
-  </si>
-  <si>
-    <t>Endurance</t>
-  </si>
-  <si>
-    <t>Agile</t>
-  </si>
-  <si>
-    <t>Attack with Sword Weapons</t>
-  </si>
-  <si>
-    <t>Attack with sword-type weapons</t>
-  </si>
-  <si>
-    <t>Staff Weapon Attack</t>
-  </si>
-  <si>
-    <t>Magic Book Weapon Attack</t>
-  </si>
-  <si>
-    <t>Additional Restoration</t>
-  </si>
-  <si>
-    <t>Daze resistance</t>
-  </si>
-  <si>
-    <t>Bow and Arrow Weapon Attack</t>
-  </si>
-  <si>
     <t>Bravery</t>
   </si>
   <si>
@@ -935,12 +821,6 @@
   </si>
   <si>
     <t>Resting Hand</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Defense</t>
-  </si>
-  <si>
-    <t>Magic Defense</t>
   </si>
   <si>
     <t>Skill damage</t>
@@ -954,6 +834,147 @@
   </si>
   <si>
     <t>c</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>Atk</t>
+  </si>
+  <si>
+    <t>Phys Def</t>
+  </si>
+  <si>
+    <t>Magic Def</t>
+  </si>
+  <si>
+    <t>Smash Add</t>
+  </si>
+  <si>
+    <t>True Dmg</t>
+  </si>
+  <si>
+    <t>Smash Rate</t>
+  </si>
+  <si>
+    <t>HP Regen/sec</t>
+  </si>
+  <si>
+    <t>Ignore Def</t>
+  </si>
+  <si>
+    <t>Ignore Magic Def</t>
+  </si>
+  <si>
+    <t>Luck</t>
+  </si>
+  <si>
+    <t>Crit Rating</t>
+  </si>
+  <si>
+    <t>Resilience Rating</t>
+  </si>
+  <si>
+    <t>Hit Rating</t>
+  </si>
+  <si>
+    <t>Dodge Rating</t>
+  </si>
+  <si>
+    <t>Crit Rate</t>
+  </si>
+  <si>
+    <t>Crit Res</t>
+  </si>
+  <si>
+    <t>Hit Rate</t>
+  </si>
+  <si>
+    <t>Dodge Rate</t>
+  </si>
+  <si>
+    <t>Atk Pen</t>
+  </si>
+  <si>
+    <t>Magic Pen</t>
+  </si>
+  <si>
+    <t>Lord Melee Bonus</t>
+  </si>
+  <si>
+    <t>Lord Skill Bonus</t>
+  </si>
+  <si>
+    <t>Lord Melee Mitigation</t>
+  </si>
+  <si>
+    <t>Lord Skill Mitigation</t>
+  </si>
+  <si>
+    <t>CD Reduction</t>
+  </si>
+  <si>
+    <t>Exp Gain</t>
+  </si>
+  <si>
+    <t>Str</t>
+  </si>
+  <si>
+    <t>Agi</t>
+  </si>
+  <si>
+    <t>Int</t>
+  </si>
+  <si>
+    <t>Stam</t>
+  </si>
+  <si>
+    <t>Vit</t>
+  </si>
+  <si>
+    <t>Blade Attack</t>
+  </si>
+  <si>
+    <t>Sword Attack</t>
+  </si>
+  <si>
+    <t>Staff Attack</t>
+  </si>
+  <si>
+    <t>Tome Attack</t>
+  </si>
+  <si>
+    <t>Bow Attack</t>
+  </si>
+  <si>
+    <t>Extra Regen</t>
+  </si>
+  <si>
+    <t>Daze resistance</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+  </si>
+  <si>
+    <t>Lucky</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic Resistance</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Smash Rate</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic Penetration</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack penetration</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -2851,7 +2872,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="11.375" customWidth="1"/>
-    <col min="4" max="5" width="18.875" customWidth="1"/>
+    <col min="4" max="4" width="18.875" customWidth="1"/>
+    <col min="5" max="5" width="38.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.875" customWidth="1"/>
     <col min="7" max="8" width="22.875" customWidth="1"/>
     <col min="9" max="9" width="11.375" customWidth="1"/>
@@ -2865,7 +2887,7 @@
     <row r="1" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E2" s="10" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="3:17" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2923,7 +2945,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
@@ -3017,7 +3039,7 @@
         <v>24</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F6" s="6">
         <v>1002</v>
@@ -3064,7 +3086,7 @@
         <v>26</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F7" s="6">
         <v>1003</v>
@@ -3111,7 +3133,7 @@
         <v>27</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="F8" s="6">
         <v>1004</v>
@@ -3158,7 +3180,7 @@
         <v>28</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="F9" s="6">
         <v>1005</v>
@@ -3205,7 +3227,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F10" s="6">
         <v>1006</v>
@@ -3252,7 +3274,7 @@
         <v>30</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F11" s="6">
         <v>1007</v>
@@ -3299,7 +3321,7 @@
         <v>31</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="F12" s="6">
         <v>1008</v>
@@ -3346,7 +3368,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="F13" s="6">
         <v>1009</v>
@@ -3393,7 +3415,7 @@
         <v>33</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="F14" s="6">
         <v>1010</v>
@@ -3440,7 +3462,7 @@
         <v>34</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="F15" s="6">
         <v>1011</v>
@@ -3487,7 +3509,7 @@
         <v>35</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="F16" s="6">
         <v>1012</v>
@@ -3534,7 +3556,7 @@
         <v>36</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="F17" s="6">
         <v>1013</v>
@@ -3581,7 +3603,7 @@
         <v>37</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="F18" s="6">
         <v>1014</v>
@@ -3628,7 +3650,7 @@
         <v>38</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
       <c r="F19" s="6">
         <v>1015</v>
@@ -3675,7 +3697,7 @@
         <v>39</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="F20" s="6">
         <v>1016</v>
@@ -3722,7 +3744,7 @@
         <v>40</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="F21" s="6">
         <v>1017</v>
@@ -3769,7 +3791,7 @@
         <v>41</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="F22" s="6">
         <v>1018</v>
@@ -3816,7 +3838,7 @@
         <v>42</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="F23" s="6">
         <v>1019</v>
@@ -3863,7 +3885,7 @@
         <v>43</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="F24" s="6">
         <v>1020</v>
@@ -3910,7 +3932,7 @@
         <v>44</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="F25" s="6">
         <v>1021</v>
@@ -3957,7 +3979,7 @@
         <v>45</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F26" s="6">
         <v>1022</v>
@@ -4004,7 +4026,7 @@
         <v>46</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F27" s="6">
         <v>1023</v>
@@ -4051,7 +4073,7 @@
         <v>47</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F28" s="6">
         <v>1024</v>
@@ -4098,7 +4120,7 @@
         <v>48</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
       <c r="F29" s="6">
         <v>1025</v>
@@ -4145,7 +4167,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F30" s="6">
         <v>1026</v>
@@ -4192,7 +4214,7 @@
         <v>50</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F31" s="6">
         <v>1027</v>
@@ -4239,7 +4261,7 @@
         <v>51</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="F32" s="6">
         <v>1028</v>
@@ -4286,7 +4308,7 @@
         <v>52</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="F33" s="6">
         <v>1030</v>
@@ -4333,7 +4355,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="F34" s="6">
         <v>1031</v>
@@ -4380,7 +4402,7 @@
         <v>54</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="F35" s="6">
         <v>1032</v>
@@ -4427,7 +4449,7 @@
         <v>55</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="F36" s="6">
         <v>1033</v>
@@ -4474,7 +4496,7 @@
         <v>56</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="F37" s="6">
         <v>1034</v>
@@ -4521,7 +4543,7 @@
         <v>57</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="F38" s="6">
         <v>1035</v>
@@ -4568,7 +4590,7 @@
         <v>58</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="F39" s="6">
         <v>1036</v>
@@ -4615,7 +4637,7 @@
         <v>59</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="F40" s="6">
         <v>1037</v>
@@ -4662,7 +4684,7 @@
         <v>60</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="F41" s="6">
         <v>1038</v>
@@ -4709,7 +4731,7 @@
         <v>61</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="F42" s="6">
         <v>1039</v>
@@ -4756,7 +4778,7 @@
         <v>62</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F43" s="6">
         <v>1040</v>
@@ -4803,7 +4825,7 @@
         <v>63</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="F44" s="6">
         <v>1041</v>
@@ -4850,7 +4872,7 @@
         <v>64</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="F45" s="6">
         <v>1042</v>
@@ -4897,7 +4919,7 @@
         <v>65</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="F46" s="6">
         <v>1043</v>
@@ -4944,7 +4966,7 @@
         <v>66</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="F47" s="6">
         <v>1044</v>
@@ -4991,7 +5013,7 @@
         <v>67</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="F48" s="6">
         <v>1045</v>
@@ -5038,7 +5060,7 @@
         <v>68</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="F49" s="6">
         <v>1046</v>
@@ -5085,7 +5107,7 @@
         <v>69</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="F50" s="6">
         <v>1047</v>
@@ -5132,7 +5154,7 @@
         <v>108</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="F51" s="6">
         <v>0</v>
@@ -5179,7 +5201,7 @@
         <v>70</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="F52" s="6">
         <v>2002</v>
@@ -5226,7 +5248,7 @@
         <v>71</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="F53" s="6">
         <v>2003</v>
@@ -5273,7 +5295,7 @@
         <v>72</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="F54" s="6">
         <v>2004</v>
@@ -5320,7 +5342,7 @@
         <v>73</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="F55" s="6">
         <v>2005</v>
@@ -5367,7 +5389,7 @@
         <v>74</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="F56" s="6">
         <v>2006</v>
@@ -5414,7 +5436,7 @@
         <v>75</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="F57" s="6">
         <v>2007</v>
@@ -5461,7 +5483,7 @@
         <v>76</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="F58" s="6">
         <v>2008</v>
@@ -5508,7 +5530,7 @@
         <v>77</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="F59" s="6">
         <v>2009</v>
@@ -5555,7 +5577,7 @@
         <v>78</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="F60" s="6">
         <v>2010</v>
@@ -5602,7 +5624,7 @@
         <v>79</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="F61" s="6">
         <v>2011</v>
@@ -5649,7 +5671,7 @@
         <v>80</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="F62" s="6">
         <v>2012</v>
@@ -5696,7 +5718,7 @@
         <v>81</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="F63" s="6">
         <v>2013</v>
@@ -5743,7 +5765,7 @@
         <v>82</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="F64" s="6">
         <v>2014</v>
@@ -5790,7 +5812,7 @@
         <v>83</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="F65" s="6">
         <v>2015</v>
@@ -5837,7 +5859,7 @@
         <v>84</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="F66" s="6">
         <v>2016</v>
@@ -5884,7 +5906,7 @@
         <v>85</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="F67" s="6">
         <v>2017</v>
@@ -5931,7 +5953,7 @@
         <v>86</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="F68" s="6">
         <v>2101</v>
@@ -5978,7 +6000,7 @@
         <v>87</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="F69" s="6">
         <v>2102</v>
@@ -6025,7 +6047,7 @@
         <v>88</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="F70" s="6">
         <v>2103</v>
@@ -6072,7 +6094,7 @@
         <v>89</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>180</v>
+        <v>142</v>
       </c>
       <c r="F71" s="6">
         <v>2104</v>
@@ -6119,7 +6141,7 @@
         <v>90</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="F72" s="6">
         <v>2105</v>
@@ -6166,7 +6188,7 @@
         <v>91</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="F73" s="6">
         <v>2106</v>
@@ -6213,7 +6235,7 @@
         <v>92</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>183</v>
+        <v>145</v>
       </c>
       <c r="F74" s="6">
         <v>2107</v>
@@ -6260,7 +6282,7 @@
         <v>93</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>184</v>
+        <v>146</v>
       </c>
       <c r="F75" s="6">
         <v>2108</v>
@@ -6307,7 +6329,7 @@
         <v>94</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="F76" s="6">
         <v>2109</v>
@@ -6354,7 +6376,7 @@
         <v>95</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>186</v>
+        <v>148</v>
       </c>
       <c r="F77" s="6">
         <v>2110</v>
@@ -6401,7 +6423,7 @@
         <v>96</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="F78" s="6">
         <v>2111</v>
@@ -6448,7 +6470,7 @@
         <v>97</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="F79" s="6">
         <v>2112</v>
@@ -6495,7 +6517,7 @@
         <v>98</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="F80" s="6">
         <v>2113</v>
@@ -6542,7 +6564,7 @@
         <v>99</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="F81" s="6">
         <v>0</v>
@@ -6590,7 +6612,7 @@
         <v>24</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F82" s="6">
         <v>0</v>
@@ -6638,7 +6660,7 @@
         <v>101</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F83" s="6">
         <v>0</v>
@@ -6686,7 +6708,7 @@
         <v>102</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F84" s="6">
         <v>0</v>
@@ -6734,7 +6756,7 @@
         <v>103</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F85" s="6">
         <v>0</v>
@@ -6782,7 +6804,7 @@
         <v>104</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F86" s="6">
         <v>0</v>
@@ -6830,7 +6852,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F87" s="6">
         <v>0</v>
@@ -6878,7 +6900,7 @@
         <v>101</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F88" s="6">
         <v>0</v>
@@ -6926,7 +6948,7 @@
         <v>102</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F89" s="6">
         <v>0</v>
@@ -6974,7 +6996,7 @@
         <v>103</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F90" s="6">
         <v>0</v>
@@ -7022,7 +7044,7 @@
         <v>104</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F91" s="6">
         <v>0</v>
@@ -7070,7 +7092,7 @@
         <v>24</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F92" s="6">
         <v>0</v>
@@ -7118,7 +7140,7 @@
         <v>101</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F93" s="6">
         <v>0</v>
@@ -7166,7 +7188,7 @@
         <v>102</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F94" s="6">
         <v>0</v>
@@ -7214,7 +7236,7 @@
         <v>103</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F95" s="6">
         <v>0</v>
@@ -7262,7 +7284,7 @@
         <v>104</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F96" s="6">
         <v>0</v>
@@ -7310,7 +7332,7 @@
         <v>24</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F97" s="6">
         <v>0</v>
@@ -7358,7 +7380,7 @@
         <v>101</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F98" s="6">
         <v>0</v>
@@ -7406,7 +7428,7 @@
         <v>102</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F99" s="6">
         <v>0</v>
@@ -7454,7 +7476,7 @@
         <v>103</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F100" s="6">
         <v>0</v>
@@ -7502,7 +7524,7 @@
         <v>104</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F101" s="6">
         <v>0</v>
@@ -7550,7 +7572,7 @@
         <v>105</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F102" s="6">
         <v>0</v>
@@ -7598,7 +7620,7 @@
         <v>101</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F103" s="6">
         <v>0</v>
@@ -7646,7 +7668,7 @@
         <v>102</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F104" s="6">
         <v>0</v>
@@ -7694,7 +7716,7 @@
         <v>103</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F105" s="6">
         <v>0</v>
@@ -7742,7 +7764,7 @@
         <v>104</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F106" s="6">
         <v>0</v>
@@ -7790,7 +7812,7 @@
         <v>24</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="F107" s="6">
         <v>0</v>
@@ -7838,7 +7860,7 @@
         <v>101</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="F108" s="6">
         <v>0</v>
@@ -7886,7 +7908,7 @@
         <v>102</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F109" s="6">
         <v>0</v>
@@ -7934,7 +7956,7 @@
         <v>103</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="F110" s="6">
         <v>0</v>
@@ -7982,7 +8004,7 @@
         <v>104</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>192</v>
+        <v>152</v>
       </c>
       <c r="F111" s="6">
         <v>0</v>
@@ -8029,7 +8051,7 @@
         <v>107</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="F112" s="6">
         <v>1013</v>
@@ -8076,7 +8098,7 @@
         <v>94</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="F113" s="6">
         <v>2109</v>
@@ -8123,7 +8145,7 @@
         <v>90</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>181</v>
+        <v>143</v>
       </c>
       <c r="F114" s="6">
         <v>2105</v>
@@ -8170,7 +8192,7 @@
         <v>91</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="F115" s="6">
         <v>2106</v>
@@ -8218,7 +8240,7 @@
         <v>101</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F116" s="6">
         <v>0</v>
@@ -8265,7 +8287,7 @@
         <v>41</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="F117" s="6">
         <v>1018</v>
@@ -8312,7 +8334,7 @@
         <v>42</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="F118" s="6">
         <v>1019</v>
@@ -8359,7 +8381,7 @@
         <v>43</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="F119" s="6">
         <v>1020</v>
@@ -8406,7 +8428,7 @@
         <v>44</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="F120" s="6">
         <v>1021</v>
@@ -8453,7 +8475,7 @@
         <v>31</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="F121" s="6">
         <v>1008</v>
@@ -8500,7 +8522,7 @@
         <v>59</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="F122" s="6">
         <v>10002</v>
@@ -8547,7 +8569,7 @@
         <v>60</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="F123" s="6">
         <v>10003</v>
@@ -8594,7 +8616,7 @@
         <v>61</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="F124" s="6">
         <v>10004</v>
@@ -8641,7 +8663,7 @@
         <v>62</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="F125" s="6">
         <v>10005</v>
@@ -8688,7 +8710,7 @@
         <v>41</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="F126" s="6">
         <v>10006</v>
@@ -8735,7 +8757,7 @@
         <v>42</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="F127" s="6">
         <v>10007</v>
@@ -8782,7 +8804,7 @@
         <v>43</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="F128" s="6">
         <v>10008</v>
@@ -8829,7 +8851,7 @@
         <v>44</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="F129" s="6">
         <v>10009</v>
@@ -8876,7 +8898,7 @@
         <v>31</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="F130" s="6">
         <v>10010</v>
@@ -8923,7 +8945,7 @@
         <v>45</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F131" s="6">
         <v>10011</v>
@@ -8970,7 +8992,7 @@
         <v>46</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F132" s="6">
         <v>10012</v>
@@ -9017,7 +9039,7 @@
         <v>47</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F133" s="6">
         <v>10013</v>
@@ -9064,7 +9086,7 @@
         <v>48</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="F134" s="6">
         <v>10014</v>
@@ -9111,7 +9133,7 @@
         <v>49</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="F135" s="6">
         <v>10015</v>
@@ -9158,7 +9180,7 @@
         <v>50</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="F136" s="6">
         <v>10016</v>
@@ -9205,7 +9227,7 @@
         <v>51</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="F137" s="6">
         <v>10017</v>
@@ -9252,7 +9274,7 @@
         <v>52</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="F138" s="6">
         <v>0</v>
@@ -9299,7 +9321,7 @@
         <v>101</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F139" s="6">
         <v>0</v>
@@ -9346,7 +9368,7 @@
         <v>109</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>193</v>
+        <v>153</v>
       </c>
       <c r="F140" s="6">
         <v>0</v>
